--- a/data/community-listings.xlsx
+++ b/data/community-listings.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4073" uniqueCount="1251">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -2166,7 +2166,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">モンスタープラネット</t>
@@ -2708,18 +2708,6 @@
   </si>
   <si>
     <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-02-15. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">com-12fb87c6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San.wich by Swee Heng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandwich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sanwich.com.sg/</t>
   </si>
   <si>
     <t xml:space="preserve">com-48dc2d18</t>
@@ -2778,7 +2766,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">食家小厨</t>
@@ -2951,6 +2939,9 @@
   </si>
   <si>
     <t xml:space="preserve">Subway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandwich</t>
   </si>
   <si>
     <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2023-05-18. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
@@ -3057,7 +3048,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="DejaVu Sans"/>
+        <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">すき家</t>
@@ -3890,7 +3881,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="DejaVu Sans"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
@@ -4296,8 +4287,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblEstablishments" displayName="tblEstablishments" ref="A1:AX212" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:AX212"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblEstablishments" displayName="tblEstablishments" ref="A1:AX211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:AX211"/>
   <tableColumns count="50">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
@@ -17836,35 +17827,35 @@
         <v>52</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>77</v>
+        <v>891</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="F161" s="1" t="str">
         <f aca="false">IF(C161="Singapore",IF(LEN(TEXT(E161,"000000"))=6,LEFT(TEXT(E161,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K161" s="11" t="s">
-        <v>891</v>
+        <v>589</v>
       </c>
       <c r="L161" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M161" s="1" t="n">
-        <v>1.373733</v>
+        <v>1.327074</v>
       </c>
       <c r="N161" s="1" t="n">
-        <v>103.948602</v>
+        <v>103.846776</v>
       </c>
       <c r="O161" s="11" t="s">
         <v>60</v>
@@ -17882,13 +17873,10 @@
         <v>63</v>
       </c>
       <c r="AK161" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM161" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN161" s="1" t="s">
         <v>892</v>
+      </c>
+      <c r="AM161" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT161" s="1" t="s">
         <v>66</v>
@@ -17915,29 +17903,17 @@
         <v>893</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>441</v>
+        <v>894</v>
       </c>
       <c r="F162" s="1" t="str">
         <f aca="false">IF(C162="Singapore",IF(LEN(TEXT(E162,"000000"))=6,LEFT(TEXT(E162,"000000"),2),""),"")</f>
-        <v>32</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J162" s="1" t="s">
-        <v>57</v>
+        <v>00</v>
       </c>
       <c r="K162" s="11" t="s">
         <v>589</v>
@@ -17946,16 +17922,16 @@
         <v>59</v>
       </c>
       <c r="M162" s="1" t="n">
-        <v>1.327074</v>
+        <v>1.317503</v>
       </c>
       <c r="N162" s="1" t="n">
-        <v>103.846776</v>
+        <v>103.89304</v>
       </c>
       <c r="O162" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P162" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>62</v>
@@ -17967,10 +17943,10 @@
         <v>63</v>
       </c>
       <c r="AK162" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="AM162" s="12" t="s">
-        <v>65</v>
+        <v>843</v>
+      </c>
+      <c r="AM162" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT162" s="1" t="s">
         <v>66</v>
@@ -17994,16 +17970,16 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="F163" s="1" t="str">
         <f aca="false">IF(C163="Singapore",IF(LEN(TEXT(E163,"000000"))=6,LEFT(TEXT(E163,"000000"),2),""),"")</f>
@@ -18016,10 +17992,10 @@
         <v>59</v>
       </c>
       <c r="M163" s="1" t="n">
-        <v>1.317503</v>
+        <v>1.354123</v>
       </c>
       <c r="N163" s="1" t="n">
-        <v>103.89304</v>
+        <v>103.945264</v>
       </c>
       <c r="O163" s="11" t="s">
         <v>60</v>
@@ -18037,7 +18013,7 @@
         <v>63</v>
       </c>
       <c r="AK163" s="1" t="s">
-        <v>843</v>
+        <v>82</v>
       </c>
       <c r="AM163" s="12" t="n">
         <v>46311</v>
@@ -18064,38 +18040,50 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F164" s="1" t="str">
         <f aca="false">IF(C164="Singapore",IF(LEN(TEXT(E164,"000000"))=6,LEFT(TEXT(E164,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>03</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="K164" s="11" t="s">
-        <v>589</v>
+        <v>900</v>
       </c>
       <c r="L164" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M164" s="1" t="n">
-        <v>1.354123</v>
+        <v>1.289368</v>
       </c>
       <c r="N164" s="1" t="n">
-        <v>103.945264</v>
+        <v>103.856911</v>
       </c>
       <c r="O164" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P164" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>62</v>
@@ -18107,7 +18095,7 @@
         <v>63</v>
       </c>
       <c r="AK164" s="1" t="s">
-        <v>82</v>
+        <v>901</v>
       </c>
       <c r="AM164" s="12" t="n">
         <v>46311</v>
@@ -18134,23 +18122,23 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="F165" s="1" t="str">
         <f aca="false">IF(C165="Singapore",IF(LEN(TEXT(E165,"000000"))=6,LEFT(TEXT(E165,"000000"),2),""),"")</f>
-        <v>03</v>
+        <v>05</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>193</v>
@@ -18161,23 +18149,21 @@
       <c r="J165" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K165" s="11" t="s">
-        <v>904</v>
-      </c>
+      <c r="K165" s="11"/>
       <c r="L165" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M165" s="1" t="n">
-        <v>1.289368</v>
+        <v>1.285243</v>
       </c>
       <c r="N165" s="1" t="n">
-        <v>103.856911</v>
+        <v>103.844971</v>
       </c>
       <c r="O165" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P165" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>62</v>
@@ -18189,10 +18175,13 @@
         <v>63</v>
       </c>
       <c r="AK165" s="1" t="s">
-        <v>905</v>
+        <v>283</v>
       </c>
       <c r="AM165" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN165" s="1" t="s">
+        <v>905</v>
       </c>
       <c r="AT165" s="1" t="s">
         <v>66</v>
@@ -18228,36 +18217,36 @@
         <v>908</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>282</v>
+        <v>86</v>
       </c>
       <c r="F166" s="1" t="str">
         <f aca="false">IF(C166="Singapore",IF(LEN(TEXT(E166,"000000"))=6,LEFT(TEXT(E166,"000000"),2),""),"")</f>
-        <v>05</v>
+        <v>67</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="K166" s="11"/>
       <c r="L166" s="11" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="M166" s="1" t="n">
-        <v>1.285243</v>
+        <v>1.387209</v>
       </c>
       <c r="N166" s="1" t="n">
-        <v>103.844971</v>
+        <v>103.761084</v>
       </c>
       <c r="O166" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P166" s="1" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>62</v>
@@ -18269,13 +18258,10 @@
         <v>63</v>
       </c>
       <c r="AK166" s="1" t="s">
-        <v>283</v>
+        <v>909</v>
       </c>
       <c r="AM166" s="12" t="n">
         <v>46311</v>
-      </c>
-      <c r="AN166" s="1" t="s">
-        <v>909</v>
       </c>
       <c r="AT166" s="1" t="s">
         <v>66</v>
@@ -18311,36 +18297,38 @@
         <v>912</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>86</v>
+        <v>913</v>
       </c>
       <c r="F167" s="1" t="str">
         <f aca="false">IF(C167="Singapore",IF(LEN(TEXT(E167,"000000"))=6,LEFT(TEXT(E167,"000000"),2),""),"")</f>
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>87</v>
+        <v>222</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>88</v>
+        <v>223</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K167" s="11"/>
+        <v>224</v>
+      </c>
+      <c r="K167" s="11" t="s">
+        <v>914</v>
+      </c>
       <c r="L167" s="11" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="M167" s="1" t="n">
-        <v>1.387209</v>
+        <v>1.300371</v>
       </c>
       <c r="N167" s="1" t="n">
-        <v>103.761084</v>
+        <v>103.859786</v>
       </c>
       <c r="O167" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P167" s="1" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>62</v>
@@ -18352,7 +18340,7 @@
         <v>63</v>
       </c>
       <c r="AK167" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="AM167" s="12" t="n">
         <v>46311</v>
@@ -18379,19 +18367,19 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="F168" s="1" t="str">
         <f aca="false">IF(C168="Singapore",IF(LEN(TEXT(E168,"000000"))=6,LEFT(TEXT(E168,"000000"),2),""),"")</f>
@@ -18407,16 +18395,16 @@
         <v>224</v>
       </c>
       <c r="K168" s="11" t="s">
-        <v>918</v>
+        <v>276</v>
       </c>
       <c r="L168" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M168" s="1" t="n">
-        <v>1.300371</v>
+        <v>1.30128</v>
       </c>
       <c r="N168" s="1" t="n">
-        <v>103.859786</v>
+        <v>103.859682</v>
       </c>
       <c r="O168" s="11" t="s">
         <v>60</v>
@@ -18434,10 +18422,13 @@
         <v>63</v>
       </c>
       <c r="AK168" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AM168" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN168" s="1" t="s">
+        <v>921</v>
       </c>
       <c r="AT168" s="1" t="s">
         <v>66</v>
@@ -18461,44 +18452,44 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="F169" s="1" t="str">
         <f aca="false">IF(C169="Singapore",IF(LEN(TEXT(E169,"000000"))=6,LEFT(TEXT(E169,"000000"),2),""),"")</f>
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>222</v>
+        <v>926</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>223</v>
+        <v>109</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="K169" s="11" t="s">
-        <v>276</v>
+        <v>927</v>
       </c>
       <c r="L169" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M169" s="1" t="n">
-        <v>1.30128</v>
+        <v>1.32035</v>
       </c>
       <c r="N169" s="1" t="n">
-        <v>103.859682</v>
+        <v>103.844145</v>
       </c>
       <c r="O169" s="11" t="s">
         <v>60</v>
@@ -18516,13 +18507,13 @@
         <v>63</v>
       </c>
       <c r="AK169" s="1" t="s">
-        <v>924</v>
+        <v>824</v>
       </c>
       <c r="AM169" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN169" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="AT169" s="1" t="s">
         <v>66</v>
@@ -18546,50 +18537,50 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="F170" s="1" t="str">
         <f aca="false">IF(C170="Singapore",IF(LEN(TEXT(E170,"000000"))=6,LEFT(TEXT(E170,"000000"),2),""),"")</f>
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>109</v>
+        <v>934</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>110</v>
+        <v>935</v>
       </c>
       <c r="K170" s="11" t="s">
-        <v>931</v>
+        <v>102</v>
       </c>
       <c r="L170" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M170" s="1" t="n">
-        <v>1.32035</v>
+        <v>1.397069</v>
       </c>
       <c r="N170" s="1" t="n">
-        <v>103.844145</v>
+        <v>103.818766</v>
       </c>
       <c r="O170" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>62</v>
@@ -18601,13 +18592,10 @@
         <v>63</v>
       </c>
       <c r="AK170" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="AM170" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN170" s="1" t="s">
-        <v>932</v>
+        <v>936</v>
+      </c>
+      <c r="AM170" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT170" s="1" t="s">
         <v>66</v>
@@ -18631,32 +18619,32 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C171" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="F171" s="1" t="str">
         <f aca="false">IF(C171="Singapore",IF(LEN(TEXT(E171,"000000"))=6,LEFT(TEXT(E171,"000000"),2),""),"")</f>
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>937</v>
+        <v>364</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>938</v>
+        <v>365</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>939</v>
+        <v>366</v>
       </c>
       <c r="K171" s="11" t="s">
         <v>102</v>
@@ -18665,16 +18653,16 @@
         <v>59</v>
       </c>
       <c r="M171" s="1" t="n">
-        <v>1.397069</v>
+        <v>1.321918</v>
       </c>
       <c r="N171" s="1" t="n">
-        <v>103.818766</v>
+        <v>103.770078</v>
       </c>
       <c r="O171" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P171" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>62</v>
@@ -18686,10 +18674,13 @@
         <v>63</v>
       </c>
       <c r="AK171" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="AM171" s="12" t="s">
-        <v>65</v>
+        <v>941</v>
+      </c>
+      <c r="AM171" s="12" t="n">
+        <v>46311</v>
+      </c>
+      <c r="AN171" s="1" t="s">
+        <v>942</v>
       </c>
       <c r="AT171" s="1" t="s">
         <v>66</v>
@@ -18713,32 +18704,32 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F172" s="1" t="str">
         <f aca="false">IF(C172="Singapore",IF(LEN(TEXT(E172,"000000"))=6,LEFT(TEXT(E172,"000000"),2),""),"")</f>
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>364</v>
+        <v>87</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>365</v>
+        <v>88</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>366</v>
+        <v>89</v>
       </c>
       <c r="K172" s="11" t="s">
         <v>102</v>
@@ -18747,16 +18738,16 @@
         <v>59</v>
       </c>
       <c r="M172" s="1" t="n">
-        <v>1.321918</v>
+        <v>1.358047</v>
       </c>
       <c r="N172" s="1" t="n">
-        <v>103.770078</v>
+        <v>103.767918</v>
       </c>
       <c r="O172" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P172" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>62</v>
@@ -18768,13 +18759,13 @@
         <v>63</v>
       </c>
       <c r="AK172" s="1" t="s">
-        <v>945</v>
+        <v>804</v>
       </c>
       <c r="AM172" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN172" s="1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="AT172" s="1" t="s">
         <v>66</v>
@@ -18798,50 +18789,50 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>942</v>
       </c>
       <c r="C173" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>948</v>
+        <v>68</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>949</v>
+        <v>69</v>
       </c>
       <c r="F173" s="1" t="str">
         <f aca="false">IF(C173="Singapore",IF(LEN(TEXT(E173,"000000"))=6,LEFT(TEXT(E173,"000000"),2),""),"")</f>
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="K173" s="11" t="s">
-        <v>102</v>
+        <v>948</v>
       </c>
       <c r="L173" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M173" s="1" t="n">
-        <v>1.358047</v>
+        <v>1.372363</v>
       </c>
       <c r="N173" s="1" t="n">
-        <v>103.767918</v>
+        <v>103.9499</v>
       </c>
       <c r="O173" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P173" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>62</v>
@@ -18853,13 +18844,13 @@
         <v>63</v>
       </c>
       <c r="AK173" s="1" t="s">
-        <v>804</v>
+        <v>79</v>
       </c>
       <c r="AM173" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN173" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="AT173" s="1" t="s">
         <v>66</v>
@@ -18892,35 +18883,35 @@
         <v>52</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>68</v>
+        <v>952</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>69</v>
+        <v>953</v>
       </c>
       <c r="F174" s="1" t="str">
         <f aca="false">IF(C174="Singapore",IF(LEN(TEXT(E174,"000000"))=6,LEFT(TEXT(E174,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>70</v>
+        <v>926</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="K174" s="11" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="L174" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M174" s="1" t="n">
-        <v>1.372363</v>
+        <v>1.320729</v>
       </c>
       <c r="N174" s="1" t="n">
-        <v>103.9499</v>
+        <v>103.844198</v>
       </c>
       <c r="O174" s="11" t="s">
         <v>60</v>
@@ -18938,13 +18929,10 @@
         <v>63</v>
       </c>
       <c r="AK174" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM174" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN174" s="1" t="s">
-        <v>953</v>
+        <v>955</v>
+      </c>
+      <c r="AM174" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT174" s="1" t="s">
         <v>66</v>
@@ -18968,44 +18956,44 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>957</v>
+        <v>625</v>
       </c>
       <c r="F175" s="1" t="str">
         <f aca="false">IF(C175="Singapore",IF(LEN(TEXT(E175,"000000"))=6,LEFT(TEXT(E175,"000000"),2),""),"")</f>
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>930</v>
+        <v>87</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="K175" s="11" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="L175" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M175" s="1" t="n">
-        <v>1.320729</v>
+        <v>1.378563</v>
       </c>
       <c r="N175" s="1" t="n">
-        <v>103.844198</v>
+        <v>103.763835</v>
       </c>
       <c r="O175" s="11" t="s">
         <v>60</v>
@@ -19023,10 +19011,13 @@
         <v>63</v>
       </c>
       <c r="AK175" s="1" t="s">
-        <v>959</v>
+        <v>610</v>
       </c>
       <c r="AM175" s="12" t="s">
         <v>65</v>
+      </c>
+      <c r="AN175" s="1" t="s">
+        <v>949</v>
       </c>
       <c r="AT175" s="1" t="s">
         <v>66</v>
@@ -19050,44 +19041,44 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>961</v>
+        <v>440</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>625</v>
+        <v>441</v>
       </c>
       <c r="F176" s="1" t="str">
         <f aca="false">IF(C176="Singapore",IF(LEN(TEXT(E176,"000000"))=6,LEFT(TEXT(E176,"000000"),2),""),"")</f>
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="K176" s="11" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="L176" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M176" s="1" t="n">
-        <v>1.378563</v>
+        <v>1.327046</v>
       </c>
       <c r="N176" s="1" t="n">
-        <v>103.763835</v>
+        <v>103.846316</v>
       </c>
       <c r="O176" s="11" t="s">
         <v>60</v>
@@ -19105,13 +19096,10 @@
         <v>63</v>
       </c>
       <c r="AK176" s="1" t="s">
-        <v>610</v>
+        <v>961</v>
       </c>
       <c r="AM176" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="AN176" s="1" t="s">
-        <v>953</v>
       </c>
       <c r="AT176" s="1" t="s">
         <v>66</v>
@@ -19138,41 +19126,41 @@
         <v>962</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>440</v>
+        <v>559</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>441</v>
+        <v>560</v>
       </c>
       <c r="F177" s="1" t="str">
         <f aca="false">IF(C177="Singapore",IF(LEN(TEXT(E177,"000000"))=6,LEFT(TEXT(E177,"000000"),2),""),"")</f>
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>56</v>
+        <v>254</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="K177" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L177" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M177" s="1" t="n">
-        <v>1.327046</v>
+        <v>1.346901</v>
       </c>
       <c r="N177" s="1" t="n">
-        <v>103.846316</v>
+        <v>103.680206</v>
       </c>
       <c r="O177" s="11" t="s">
         <v>60</v>
@@ -19190,10 +19178,10 @@
         <v>63</v>
       </c>
       <c r="AK177" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="AM177" s="12" t="s">
-        <v>65</v>
+        <v>963</v>
+      </c>
+      <c r="AM177" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT177" s="1" t="s">
         <v>66</v>
@@ -19217,44 +19205,44 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>559</v>
+        <v>68</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>560</v>
+        <v>69</v>
       </c>
       <c r="F178" s="1" t="str">
         <f aca="false">IF(C178="Singapore",IF(LEN(TEXT(E178,"000000"))=6,LEFT(TEXT(E178,"000000"),2),""),"")</f>
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>254</v>
+        <v>71</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>255</v>
+        <v>72</v>
       </c>
       <c r="K178" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L178" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M178" s="1" t="n">
-        <v>1.346901</v>
+        <v>1.372388</v>
       </c>
       <c r="N178" s="1" t="n">
-        <v>103.680206</v>
+        <v>103.949975</v>
       </c>
       <c r="O178" s="11" t="s">
         <v>60</v>
@@ -19272,10 +19260,13 @@
         <v>63</v>
       </c>
       <c r="AK178" s="1" t="s">
-        <v>966</v>
+        <v>79</v>
       </c>
       <c r="AM178" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN178" s="1" t="s">
+        <v>965</v>
       </c>
       <c r="AT178" s="1" t="s">
         <v>66</v>
@@ -19299,44 +19290,44 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>68</v>
+        <v>967</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>69</v>
+        <v>968</v>
       </c>
       <c r="F179" s="1" t="str">
         <f aca="false">IF(C179="Singapore",IF(LEN(TEXT(E179,"000000"))=6,LEFT(TEXT(E179,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>70</v>
+        <v>267</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>71</v>
+        <v>268</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>72</v>
+        <v>269</v>
       </c>
       <c r="K179" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L179" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M179" s="1" t="n">
-        <v>1.372388</v>
+        <v>1.301718</v>
       </c>
       <c r="N179" s="1" t="n">
-        <v>103.949975</v>
+        <v>103.905945</v>
       </c>
       <c r="O179" s="11" t="s">
         <v>60</v>
@@ -19354,13 +19345,10 @@
         <v>63</v>
       </c>
       <c r="AK179" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM179" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN179" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
+      </c>
+      <c r="AM179" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT179" s="1" t="s">
         <v>66</v>
@@ -19384,44 +19372,44 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>971</v>
+        <v>192</v>
       </c>
       <c r="F180" s="1" t="str">
         <f aca="false">IF(C180="Singapore",IF(LEN(TEXT(E180,"000000"))=6,LEFT(TEXT(E180,"000000"),2),""),"")</f>
-        <v>44</v>
+        <v>03</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="K180" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L180" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M180" s="1" t="n">
-        <v>1.301718</v>
+        <v>1.289907</v>
       </c>
       <c r="N180" s="1" t="n">
-        <v>103.905945</v>
+        <v>103.856123</v>
       </c>
       <c r="O180" s="11" t="s">
         <v>60</v>
@@ -19441,8 +19429,8 @@
       <c r="AK180" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="AM180" s="12" t="s">
-        <v>65</v>
+      <c r="AM180" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT180" s="1" t="s">
         <v>66</v>
@@ -19469,7 +19457,7 @@
         <v>973</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>52</v>
@@ -19478,11 +19466,11 @@
         <v>974</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="F181" s="1" t="str">
         <f aca="false">IF(C181="Singapore",IF(LEN(TEXT(E181,"000000"))=6,LEFT(TEXT(E181,"000000"),2),""),"")</f>
-        <v>03</v>
+        <v>05</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>193</v>
@@ -19494,22 +19482,22 @@
         <v>195</v>
       </c>
       <c r="K181" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L181" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M181" s="1" t="n">
-        <v>1.289907</v>
+        <v>1.285616</v>
       </c>
       <c r="N181" s="1" t="n">
-        <v>103.856123</v>
+        <v>103.845019</v>
       </c>
       <c r="O181" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P181" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>62</v>
@@ -19551,7 +19539,7 @@
         <v>976</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>52</v>
@@ -19560,38 +19548,38 @@
         <v>977</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>282</v>
+        <v>978</v>
       </c>
       <c r="F182" s="1" t="str">
         <f aca="false">IF(C182="Singapore",IF(LEN(TEXT(E182,"000000"))=6,LEFT(TEXT(E182,"000000"),2),""),"")</f>
-        <v>05</v>
+        <v>64</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="K182" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L182" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M182" s="1" t="n">
-        <v>1.285616</v>
+        <v>1.339961</v>
       </c>
       <c r="N182" s="1" t="n">
-        <v>103.845019</v>
+        <v>103.706317</v>
       </c>
       <c r="O182" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P182" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>62</v>
@@ -19603,10 +19591,10 @@
         <v>63</v>
       </c>
       <c r="AK182" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="AM182" s="12" t="n">
-        <v>46311</v>
+        <v>979</v>
+      </c>
+      <c r="AM182" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT182" s="1" t="s">
         <v>66</v>
@@ -19630,44 +19618,32 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C183" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="E183" s="1" t="s">
         <v>981</v>
       </c>
       <c r="F183" s="1" t="str">
         <f aca="false">IF(C183="Singapore",IF(LEN(TEXT(E183,"000000"))=6,LEFT(TEXT(E183,"000000"),2),""),"")</f>
-        <v>64</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="J183" s="1" t="s">
-        <v>255</v>
+        <v>00</v>
       </c>
       <c r="K183" s="11" t="s">
-        <v>891</v>
+        <v>960</v>
       </c>
       <c r="L183" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M183" s="1" t="n">
-        <v>1.339961</v>
+        <v>1.366996</v>
       </c>
       <c r="N183" s="1" t="n">
-        <v>103.706317</v>
+        <v>103.964659</v>
       </c>
       <c r="O183" s="11" t="s">
         <v>60</v>
@@ -19687,8 +19663,8 @@
       <c r="AK183" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AM183" s="12" t="s">
-        <v>65</v>
+      <c r="AM183" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT183" s="1" t="s">
         <v>66</v>
@@ -19715,35 +19691,47 @@
         <v>983</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>963</v>
+        <v>984</v>
       </c>
       <c r="C184" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>829</v>
       </c>
       <c r="F184" s="1" t="str">
         <f aca="false">IF(C184="Singapore",IF(LEN(TEXT(E184,"000000"))=6,LEFT(TEXT(E184,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>79</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>832</v>
       </c>
       <c r="K184" s="11" t="s">
-        <v>891</v>
+        <v>986</v>
       </c>
       <c r="L184" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M184" s="1" t="n">
-        <v>1.366996</v>
+        <v>1.39205</v>
       </c>
       <c r="N184" s="1" t="n">
-        <v>103.964659</v>
+        <v>103.875954</v>
       </c>
       <c r="O184" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P184" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>62</v>
@@ -19755,10 +19743,13 @@
         <v>63</v>
       </c>
       <c r="AK184" s="1" t="s">
-        <v>985</v>
+        <v>833</v>
       </c>
       <c r="AM184" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN184" s="1" t="s">
+        <v>987</v>
       </c>
       <c r="AT184" s="1" t="s">
         <v>66</v>
@@ -19782,32 +19773,32 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>988</v>
+        <v>68</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>829</v>
+        <v>69</v>
       </c>
       <c r="F185" s="1" t="str">
         <f aca="false">IF(C185="Singapore",IF(LEN(TEXT(E185,"000000"))=6,LEFT(TEXT(E185,"000000"),2),""),"")</f>
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>830</v>
+        <v>70</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>831</v>
+        <v>71</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>832</v>
+        <v>72</v>
       </c>
       <c r="K185" s="11" t="s">
         <v>989</v>
@@ -19816,16 +19807,16 @@
         <v>59</v>
       </c>
       <c r="M185" s="1" t="n">
-        <v>1.39205</v>
+        <v>1.372261</v>
       </c>
       <c r="N185" s="1" t="n">
-        <v>103.875954</v>
+        <v>103.949944</v>
       </c>
       <c r="O185" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P185" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>62</v>
@@ -19837,13 +19828,13 @@
         <v>63</v>
       </c>
       <c r="AK185" s="1" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="AM185" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN185" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="AT185" s="1" t="s">
         <v>66</v>
@@ -19867,50 +19858,50 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>987</v>
       </c>
       <c r="C186" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>68</v>
+        <v>992</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>69</v>
+        <v>993</v>
       </c>
       <c r="F186" s="1" t="str">
         <f aca="false">IF(C186="Singapore",IF(LEN(TEXT(E186,"000000"))=6,LEFT(TEXT(E186,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>03</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="K186" s="11" t="s">
-        <v>992</v>
+        <v>414</v>
       </c>
       <c r="L186" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M186" s="1" t="n">
-        <v>1.372261</v>
+        <v>1.291887</v>
       </c>
       <c r="N186" s="1" t="n">
-        <v>103.949944</v>
+        <v>103.856338</v>
       </c>
       <c r="O186" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P186" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>62</v>
@@ -19922,13 +19913,13 @@
         <v>63</v>
       </c>
       <c r="AK186" s="1" t="s">
-        <v>838</v>
+        <v>994</v>
       </c>
       <c r="AM186" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN186" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="AT186" s="1" t="s">
         <v>66</v>
@@ -19952,32 +19943,20 @@
     </row>
     <row r="187" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C187" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="E187" s="1" t="s">
         <v>996</v>
       </c>
       <c r="F187" s="1" t="str">
         <f aca="false">IF(C187="Singapore",IF(LEN(TEXT(E187,"000000"))=6,LEFT(TEXT(E187,"000000"),2),""),"")</f>
-        <v>03</v>
-      </c>
-      <c r="H187" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I187" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J187" s="1" t="s">
-        <v>195</v>
+        <v>00</v>
       </c>
       <c r="K187" s="11" t="s">
         <v>414</v>
@@ -19986,10 +19965,10 @@
         <v>59</v>
       </c>
       <c r="M187" s="1" t="n">
-        <v>1.291887</v>
+        <v>1.291438</v>
       </c>
       <c r="N187" s="1" t="n">
-        <v>103.856338</v>
+        <v>103.850192</v>
       </c>
       <c r="O187" s="11" t="s">
         <v>60</v>
@@ -20011,9 +19990,6 @@
       </c>
       <c r="AM187" s="12" t="n">
         <v>46311</v>
-      </c>
-      <c r="AN187" s="1" t="s">
-        <v>990</v>
       </c>
       <c r="AT187" s="1" t="s">
         <v>66</v>
@@ -20040,35 +20016,47 @@
         <v>998</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>1001</v>
       </c>
       <c r="F188" s="1" t="str">
         <f aca="false">IF(C188="Singapore",IF(LEN(TEXT(E188,"000000"))=6,LEFT(TEXT(E188,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>18</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="K188" s="11" t="s">
-        <v>414</v>
+        <v>1002</v>
       </c>
       <c r="L188" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M188" s="1" t="n">
-        <v>1.291438</v>
+        <v>1.296951</v>
       </c>
       <c r="N188" s="1" t="n">
-        <v>103.850192</v>
+        <v>103.857699</v>
       </c>
       <c r="O188" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P188" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R188" s="1" t="s">
         <v>62</v>
@@ -20080,7 +20068,7 @@
         <v>63</v>
       </c>
       <c r="AK188" s="1" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="AM188" s="12" t="n">
         <v>46311</v>
@@ -20107,44 +20095,44 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1003</v>
+        <v>68</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>1004</v>
+        <v>69</v>
       </c>
       <c r="F189" s="1" t="str">
         <f aca="false">IF(C189="Singapore",IF(LEN(TEXT(E189,"000000"))=6,LEFT(TEXT(E189,"000000"),2),""),"")</f>
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>224</v>
+        <v>72</v>
       </c>
       <c r="K189" s="11" t="s">
-        <v>1005</v>
+        <v>485</v>
       </c>
       <c r="L189" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M189" s="1" t="n">
-        <v>1.296951</v>
+        <v>1.372421</v>
       </c>
       <c r="N189" s="1" t="n">
-        <v>103.857699</v>
+        <v>103.94969</v>
       </c>
       <c r="O189" s="11" t="s">
         <v>60</v>
@@ -20162,10 +20150,13 @@
         <v>63</v>
       </c>
       <c r="AK189" s="1" t="s">
-        <v>1006</v>
+        <v>838</v>
       </c>
       <c r="AM189" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN189" s="1" t="s">
+        <v>1006</v>
       </c>
       <c r="AT189" s="1" t="s">
         <v>66</v>
@@ -20198,35 +20189,21 @@
         <v>52</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>69</v>
+        <v>1009</v>
       </c>
       <c r="F190" s="1" t="str">
         <f aca="false">IF(C190="Singapore",IF(LEN(TEXT(E190,"000000"))=6,LEFT(TEXT(E190,"000000"),2),""),"")</f>
-        <v>51</v>
-      </c>
-      <c r="H190" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I190" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K190" s="11" t="s">
-        <v>485</v>
-      </c>
+        <v>00</v>
+      </c>
+      <c r="K190" s="11"/>
       <c r="L190" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M190" s="1" t="n">
-        <v>1.372421</v>
+        <v>1.333967</v>
       </c>
       <c r="N190" s="1" t="n">
-        <v>103.94969</v>
+        <v>103.746882</v>
       </c>
       <c r="O190" s="11" t="s">
         <v>60</v>
@@ -20244,13 +20221,10 @@
         <v>63</v>
       </c>
       <c r="AK190" s="1" t="s">
-        <v>838</v>
+        <v>202</v>
       </c>
       <c r="AM190" s="12" t="n">
         <v>46311</v>
-      </c>
-      <c r="AN190" s="1" t="s">
-        <v>1009</v>
       </c>
       <c r="AT190" s="1" t="s">
         <v>66</v>
@@ -20285,19 +20259,31 @@
       <c r="D191" s="1" t="s">
         <v>1012</v>
       </c>
+      <c r="E191" s="1" t="s">
+        <v>1013</v>
+      </c>
       <c r="F191" s="1" t="str">
         <f aca="false">IF(C191="Singapore",IF(LEN(TEXT(E191,"000000"))=6,LEFT(TEXT(E191,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>18</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="K191" s="11"/>
       <c r="L191" s="11" t="s">
-        <v>59</v>
+        <v>197</v>
       </c>
       <c r="M191" s="1" t="n">
-        <v>1.333967</v>
+        <v>1.300284</v>
       </c>
       <c r="N191" s="1" t="n">
-        <v>103.746882</v>
+        <v>103.852079</v>
       </c>
       <c r="O191" s="11" t="s">
         <v>60</v>
@@ -20315,10 +20301,10 @@
         <v>63</v>
       </c>
       <c r="AK191" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="AM191" s="12" t="n">
-        <v>46311</v>
+        <v>1014</v>
+      </c>
+      <c r="AM191" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT191" s="1" t="s">
         <v>66</v>
@@ -20342,48 +20328,38 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F192" s="1" t="str">
         <f aca="false">IF(C192="Singapore",IF(LEN(TEXT(E192,"000000"))=6,LEFT(TEXT(E192,"000000"),2),""),"")</f>
-        <v>18</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="J192" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K192" s="11"/>
+        <v>00</v>
+      </c>
+      <c r="K192" s="11" t="s">
+        <v>1018</v>
+      </c>
       <c r="L192" s="11" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="M192" s="1" t="n">
-        <v>1.300284</v>
+        <v>1.297019</v>
       </c>
       <c r="N192" s="1" t="n">
-        <v>103.852079</v>
+        <v>103.852483</v>
       </c>
       <c r="O192" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P192" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>62</v>
@@ -20395,10 +20371,10 @@
         <v>63</v>
       </c>
       <c r="AK192" s="1" t="s">
-        <v>1017</v>
-      </c>
-      <c r="AM192" s="12" t="s">
-        <v>65</v>
+        <v>1019</v>
+      </c>
+      <c r="AM192" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT192" s="1" t="s">
         <v>66</v>
@@ -20422,32 +20398,42 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1020</v>
+        <v>1022</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>1023</v>
       </c>
       <c r="F193" s="1" t="str">
         <f aca="false">IF(C193="Singapore",IF(LEN(TEXT(E193,"000000"))=6,LEFT(TEXT(E193,"000000"),2),""),"")</f>
-        <v>00</v>
-      </c>
-      <c r="K193" s="11" t="s">
-        <v>1021</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="K193" s="11"/>
       <c r="L193" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M193" s="1" t="n">
-        <v>1.297019</v>
+        <v>1.397727</v>
       </c>
       <c r="N193" s="1" t="n">
-        <v>103.852483</v>
+        <v>103.873349</v>
       </c>
       <c r="O193" s="11" t="s">
         <v>60</v>
@@ -20465,7 +20451,7 @@
         <v>63</v>
       </c>
       <c r="AK193" s="1" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="AM193" s="12" t="n">
         <v>46311</v>
@@ -20492,48 +20478,50 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1025</v>
+        <v>77</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>1026</v>
+        <v>78</v>
       </c>
       <c r="F194" s="1" t="str">
         <f aca="false">IF(C194="Singapore",IF(LEN(TEXT(E194,"000000"))=6,LEFT(TEXT(E194,"000000"),2),""),"")</f>
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>830</v>
+        <v>70</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>831</v>
+        <v>71</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="K194" s="11"/>
+        <v>72</v>
+      </c>
+      <c r="K194" s="11" t="s">
+        <v>241</v>
+      </c>
       <c r="L194" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M194" s="1" t="n">
-        <v>1.397727</v>
+        <v>1.373953</v>
       </c>
       <c r="N194" s="1" t="n">
-        <v>103.873349</v>
+        <v>103.948462</v>
       </c>
       <c r="O194" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P194" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>62</v>
@@ -20545,10 +20533,13 @@
         <v>63</v>
       </c>
       <c r="AK194" s="1" t="s">
-        <v>1027</v>
+        <v>79</v>
       </c>
       <c r="AM194" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN194" s="1" t="s">
+        <v>1027</v>
       </c>
       <c r="AT194" s="1" t="s">
         <v>66</v>
@@ -20581,10 +20572,10 @@
         <v>52</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F195" s="1" t="str">
         <f aca="false">IF(C195="Singapore",IF(LEN(TEXT(E195,"000000"))=6,LEFT(TEXT(E195,"000000"),2),""),"")</f>
@@ -20600,16 +20591,16 @@
         <v>72</v>
       </c>
       <c r="K195" s="11" t="s">
-        <v>241</v>
+        <v>589</v>
       </c>
       <c r="L195" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M195" s="1" t="n">
-        <v>1.373953</v>
+        <v>1.372346</v>
       </c>
       <c r="N195" s="1" t="n">
-        <v>103.948462</v>
+        <v>103.949413</v>
       </c>
       <c r="O195" s="11" t="s">
         <v>60</v>
@@ -20627,7 +20618,7 @@
         <v>63</v>
       </c>
       <c r="AK195" s="1" t="s">
-        <v>79</v>
+        <v>838</v>
       </c>
       <c r="AM195" s="12" t="n">
         <v>46311</v>
@@ -20666,35 +20657,33 @@
         <v>52</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>68</v>
+        <v>1033</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>69</v>
+        <v>1034</v>
       </c>
       <c r="F196" s="1" t="str">
         <f aca="false">IF(C196="Singapore",IF(LEN(TEXT(E196,"000000"))=6,LEFT(TEXT(E196,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>70</v>
+        <v>222</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>71</v>
+        <v>223</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K196" s="11" t="s">
-        <v>589</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="K196" s="11"/>
       <c r="L196" s="11" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="M196" s="1" t="n">
-        <v>1.372346</v>
+        <v>1.30111</v>
       </c>
       <c r="N196" s="1" t="n">
-        <v>103.949413</v>
+        <v>103.85876</v>
       </c>
       <c r="O196" s="11" t="s">
         <v>60</v>
@@ -20712,13 +20701,10 @@
         <v>63</v>
       </c>
       <c r="AK196" s="1" t="s">
-        <v>838</v>
+        <v>1035</v>
       </c>
       <c r="AM196" s="12" t="n">
         <v>46311</v>
-      </c>
-      <c r="AN196" s="1" t="s">
-        <v>1033</v>
       </c>
       <c r="AT196" s="1" t="s">
         <v>66</v>
@@ -20742,48 +20728,48 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F197" s="1" t="str">
         <f aca="false">IF(C197="Singapore",IF(LEN(TEXT(E197,"000000"))=6,LEFT(TEXT(E197,"000000"),2),""),"")</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>222</v>
+        <v>565</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>223</v>
+        <v>566</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>224</v>
+        <v>567</v>
       </c>
       <c r="K197" s="11"/>
       <c r="L197" s="11" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>1.30111</v>
+        <v>1.311361</v>
       </c>
       <c r="N197" s="1" t="n">
-        <v>103.85876</v>
+        <v>103.814987</v>
       </c>
       <c r="O197" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P197" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="R197" s="1" t="s">
         <v>62</v>
@@ -20795,10 +20781,13 @@
         <v>63</v>
       </c>
       <c r="AK197" s="1" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="AM197" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN197" s="1" t="s">
+        <v>1041</v>
       </c>
       <c r="AT197" s="1" t="s">
         <v>66</v>
@@ -20822,42 +20811,42 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F198" s="1" t="str">
         <f aca="false">IF(C198="Singapore",IF(LEN(TEXT(E198,"000000"))=6,LEFT(TEXT(E198,"000000"),2),""),"")</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>565</v>
+        <v>222</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>566</v>
+        <v>223</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>567</v>
+        <v>224</v>
       </c>
       <c r="K198" s="11"/>
       <c r="L198" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>1.311361</v>
+        <v>1.300943</v>
       </c>
       <c r="N198" s="1" t="n">
-        <v>103.814987</v>
+        <v>103.859982</v>
       </c>
       <c r="O198" s="11" t="s">
         <v>60</v>
@@ -20875,13 +20864,10 @@
         <v>63</v>
       </c>
       <c r="AK198" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="AM198" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN198" s="1" t="s">
-        <v>1044</v>
+        <v>1046</v>
+      </c>
+      <c r="AM198" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT198" s="1" t="s">
         <v>66</v>
@@ -20905,48 +20891,50 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F199" s="1" t="str">
         <f aca="false">IF(C199="Singapore",IF(LEN(TEXT(E199,"000000"))=6,LEFT(TEXT(E199,"000000"),2),""),"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>222</v>
+        <v>338</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>223</v>
+        <v>339</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K199" s="11"/>
+        <v>340</v>
+      </c>
+      <c r="K199" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="L199" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>1.300943</v>
+        <v>1.304639</v>
       </c>
       <c r="N199" s="1" t="n">
-        <v>103.859982</v>
+        <v>103.854104</v>
       </c>
       <c r="O199" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P199" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R199" s="1" t="s">
         <v>62</v>
@@ -20958,10 +20946,13 @@
         <v>63</v>
       </c>
       <c r="AK199" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AM199" s="12" t="s">
         <v>65</v>
+      </c>
+      <c r="AN199" s="1" t="s">
+        <v>1051</v>
       </c>
       <c r="AT199" s="1" t="s">
         <v>66</v>
@@ -20985,44 +20976,44 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F200" s="1" t="str">
         <f aca="false">IF(C200="Singapore",IF(LEN(TEXT(E200,"000000"))=6,LEFT(TEXT(E200,"000000"),2),""),"")</f>
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>338</v>
+        <v>830</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>339</v>
+        <v>831</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>340</v>
+        <v>832</v>
       </c>
       <c r="K200" s="11" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L200" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M200" s="1" t="n">
-        <v>1.304639</v>
+        <v>1.398201</v>
       </c>
       <c r="N200" s="1" t="n">
-        <v>103.854104</v>
+        <v>103.873284</v>
       </c>
       <c r="O200" s="11" t="s">
         <v>60</v>
@@ -21040,13 +21031,10 @@
         <v>63</v>
       </c>
       <c r="AK200" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="AM200" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN200" s="1" t="s">
-        <v>1054</v>
+        <v>1024</v>
+      </c>
+      <c r="AM200" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT200" s="1" t="s">
         <v>66</v>
@@ -21070,44 +21058,44 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F201" s="1" t="str">
         <f aca="false">IF(C201="Singapore",IF(LEN(TEXT(E201,"000000"))=6,LEFT(TEXT(E201,"000000"),2),""),"")</f>
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>830</v>
+        <v>173</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>831</v>
+        <v>174</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>832</v>
+        <v>175</v>
       </c>
       <c r="K201" s="11" t="s">
-        <v>102</v>
+        <v>589</v>
       </c>
       <c r="L201" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M201" s="1" t="n">
-        <v>1.398201</v>
+        <v>1.343191</v>
       </c>
       <c r="N201" s="1" t="n">
-        <v>103.873284</v>
+        <v>103.775138</v>
       </c>
       <c r="O201" s="11" t="s">
         <v>60</v>
@@ -21125,10 +21113,13 @@
         <v>63</v>
       </c>
       <c r="AK201" s="1" t="s">
-        <v>1027</v>
+        <v>176</v>
       </c>
       <c r="AM201" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN201" s="1" t="s">
+        <v>1060</v>
       </c>
       <c r="AT201" s="1" t="s">
         <v>66</v>
@@ -21152,44 +21143,44 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>1061</v>
+        <v>68</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>1062</v>
+        <v>69</v>
       </c>
       <c r="F202" s="1" t="str">
         <f aca="false">IF(C202="Singapore",IF(LEN(TEXT(E202,"000000"))=6,LEFT(TEXT(E202,"000000"),2),""),"")</f>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="K202" s="11" t="s">
-        <v>589</v>
+        <v>1063</v>
       </c>
       <c r="L202" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M202" s="1" t="n">
-        <v>1.343191</v>
+        <v>1.372362</v>
       </c>
       <c r="N202" s="1" t="n">
-        <v>103.775138</v>
+        <v>103.949708</v>
       </c>
       <c r="O202" s="11" t="s">
         <v>60</v>
@@ -21207,13 +21198,13 @@
         <v>63</v>
       </c>
       <c r="AK202" s="1" t="s">
-        <v>176</v>
+        <v>838</v>
       </c>
       <c r="AM202" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN202" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="AT202" s="1" t="s">
         <v>66</v>
@@ -21237,44 +21228,44 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>68</v>
+        <v>1067</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>69</v>
+        <v>1068</v>
       </c>
       <c r="F203" s="1" t="str">
         <f aca="false">IF(C203="Singapore",IF(LEN(TEXT(E203,"000000"))=6,LEFT(TEXT(E203,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K203" s="11" t="s">
-        <v>1066</v>
+        <v>90</v>
       </c>
       <c r="L203" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M203" s="1" t="n">
-        <v>1.372362</v>
+        <v>1.378679</v>
       </c>
       <c r="N203" s="1" t="n">
-        <v>103.949708</v>
+        <v>103.773381</v>
       </c>
       <c r="O203" s="11" t="s">
         <v>60</v>
@@ -21292,13 +21283,10 @@
         <v>63</v>
       </c>
       <c r="AK203" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="AM203" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN203" s="1" t="s">
-        <v>1067</v>
+        <v>1069</v>
+      </c>
+      <c r="AM203" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT203" s="1" t="s">
         <v>66</v>
@@ -21322,44 +21310,42 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>1070</v>
+        <v>741</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>1071</v>
+        <v>742</v>
       </c>
       <c r="F204" s="1" t="str">
         <f aca="false">IF(C204="Singapore",IF(LEN(TEXT(E204,"000000"))=6,LEFT(TEXT(E204,"000000"),2),""),"")</f>
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>87</v>
+        <v>364</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>88</v>
+        <v>365</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K204" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="K204" s="11"/>
       <c r="L204" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M204" s="1" t="n">
-        <v>1.378679</v>
+        <v>1.294612</v>
       </c>
       <c r="N204" s="1" t="n">
-        <v>103.773381</v>
+        <v>103.772348</v>
       </c>
       <c r="O204" s="11" t="s">
         <v>60</v>
@@ -21377,10 +21363,10 @@
         <v>63</v>
       </c>
       <c r="AK204" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="AM204" s="12" t="s">
-        <v>65</v>
+        <v>743</v>
+      </c>
+      <c r="AM204" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT204" s="1" t="s">
         <v>66</v>
@@ -21404,48 +21390,48 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>1074</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>741</v>
+        <v>1074</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>742</v>
+        <v>206</v>
       </c>
       <c r="F205" s="1" t="str">
         <f aca="false">IF(C205="Singapore",IF(LEN(TEXT(E205,"000000"))=6,LEFT(TEXT(E205,"000000"),2),""),"")</f>
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>364</v>
+        <v>55</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>365</v>
+        <v>56</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>366</v>
+        <v>57</v>
       </c>
       <c r="K205" s="11"/>
       <c r="L205" s="11" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="M205" s="1" t="n">
-        <v>1.294612</v>
+        <v>1.323066</v>
       </c>
       <c r="N205" s="1" t="n">
-        <v>103.772348</v>
+        <v>103.854999</v>
       </c>
       <c r="O205" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P205" s="1" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>62</v>
@@ -21457,7 +21443,7 @@
         <v>63</v>
       </c>
       <c r="AK205" s="1" t="s">
-        <v>743</v>
+        <v>1075</v>
       </c>
       <c r="AM205" s="12" t="n">
         <v>46311</v>
@@ -21484,48 +21470,38 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>206</v>
+        <v>1078</v>
       </c>
       <c r="F206" s="1" t="str">
         <f aca="false">IF(C206="Singapore",IF(LEN(TEXT(E206,"000000"))=6,LEFT(TEXT(E206,"000000"),2),""),"")</f>
-        <v>32</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J206" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K206" s="11"/>
+        <v>00</v>
+      </c>
+      <c r="K206" s="11" t="s">
+        <v>1079</v>
+      </c>
       <c r="L206" s="11" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="M206" s="1" t="n">
-        <v>1.323066</v>
+        <v>1.263442</v>
       </c>
       <c r="N206" s="1" t="n">
-        <v>103.854999</v>
+        <v>103.821891</v>
       </c>
       <c r="O206" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P206" s="1" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>62</v>
@@ -21537,7 +21513,7 @@
         <v>63</v>
       </c>
       <c r="AK206" s="1" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="AM206" s="12" t="n">
         <v>46311</v>
@@ -21564,32 +21540,44 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>1084</v>
       </c>
       <c r="F207" s="1" t="str">
         <f aca="false">IF(C207="Singapore",IF(LEN(TEXT(E207,"000000"))=6,LEFT(TEXT(E207,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>82</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="K207" s="11" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="L207" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M207" s="1" t="n">
-        <v>1.263442</v>
+        <v>1.40596</v>
       </c>
       <c r="N207" s="1" t="n">
-        <v>103.821891</v>
+        <v>103.902377</v>
       </c>
       <c r="O207" s="11" t="s">
         <v>60</v>
@@ -21607,7 +21595,7 @@
         <v>63</v>
       </c>
       <c r="AK207" s="1" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="AM207" s="12" t="n">
         <v>46311</v>
@@ -21634,44 +21622,44 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1086</v>
+        <v>68</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>1087</v>
+        <v>69</v>
       </c>
       <c r="F208" s="1" t="str">
         <f aca="false">IF(C208="Singapore",IF(LEN(TEXT(E208,"000000"))=6,LEFT(TEXT(E208,"000000"),2),""),"")</f>
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1088</v>
+        <v>70</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>492</v>
+        <v>71</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>493</v>
+        <v>72</v>
       </c>
       <c r="K208" s="11" t="s">
-        <v>1089</v>
+        <v>399</v>
       </c>
       <c r="L208" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M208" s="1" t="n">
-        <v>1.40596</v>
+        <v>1.372316</v>
       </c>
       <c r="N208" s="1" t="n">
-        <v>103.902377</v>
+        <v>103.949925</v>
       </c>
       <c r="O208" s="11" t="s">
         <v>60</v>
@@ -21689,10 +21677,13 @@
         <v>63</v>
       </c>
       <c r="AK208" s="1" t="s">
-        <v>1090</v>
+        <v>79</v>
       </c>
       <c r="AM208" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN208" s="1" t="s">
+        <v>1089</v>
       </c>
       <c r="AT208" s="1" t="s">
         <v>66</v>
@@ -21716,44 +21707,32 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>1091</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>1085</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>69</v>
+        <v>1092</v>
       </c>
       <c r="F209" s="1" t="str">
         <f aca="false">IF(C209="Singapore",IF(LEN(TEXT(E209,"000000"))=6,LEFT(TEXT(E209,"000000"),2),""),"")</f>
-        <v>51</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I209" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J209" s="1" t="s">
-        <v>72</v>
+        <v>00</v>
       </c>
       <c r="K209" s="11" t="s">
-        <v>399</v>
+        <v>102</v>
       </c>
       <c r="L209" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M209" s="1" t="n">
-        <v>1.372316</v>
+        <v>1.305888</v>
       </c>
       <c r="N209" s="1" t="n">
-        <v>103.949925</v>
+        <v>103.850594</v>
       </c>
       <c r="O209" s="11" t="s">
         <v>60</v>
@@ -21771,13 +21750,10 @@
         <v>63</v>
       </c>
       <c r="AK209" s="1" t="s">
-        <v>79</v>
+        <v>1093</v>
       </c>
       <c r="AM209" s="12" t="n">
         <v>46311</v>
-      </c>
-      <c r="AN209" s="1" t="s">
-        <v>1092</v>
       </c>
       <c r="AT209" s="1" t="s">
         <v>66</v>
@@ -21801,32 +21777,44 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1095</v>
+        <v>68</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="F210" s="1" t="str">
         <f aca="false">IF(C210="Singapore",IF(LEN(TEXT(E210,"000000"))=6,LEFT(TEXT(E210,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>51</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="K210" s="11" t="s">
-        <v>102</v>
+        <v>414</v>
       </c>
       <c r="L210" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M210" s="1" t="n">
-        <v>1.305888</v>
+        <v>1.372381</v>
       </c>
       <c r="N210" s="1" t="n">
-        <v>103.850594</v>
+        <v>103.949343</v>
       </c>
       <c r="O210" s="11" t="s">
         <v>60</v>
@@ -21844,10 +21832,13 @@
         <v>63</v>
       </c>
       <c r="AK210" s="1" t="s">
-        <v>1096</v>
+        <v>651</v>
       </c>
       <c r="AM210" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN210" s="1" t="s">
+        <v>1096</v>
       </c>
       <c r="AT210" s="1" t="s">
         <v>66</v>
@@ -21880,41 +21871,39 @@
         <v>52</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>68</v>
+        <v>1067</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>69</v>
+        <v>1068</v>
       </c>
       <c r="F211" s="1" t="str">
         <f aca="false">IF(C211="Singapore",IF(LEN(TEXT(E211,"000000"))=6,LEFT(TEXT(E211,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K211" s="11" t="s">
-        <v>414</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="K211" s="11"/>
       <c r="L211" s="11" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="M211" s="1" t="n">
-        <v>1.372381</v>
+        <v>1.378723</v>
       </c>
       <c r="N211" s="1" t="n">
-        <v>103.949343</v>
+        <v>103.773386</v>
       </c>
       <c r="O211" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P211" s="1" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>62</v>
@@ -21926,13 +21915,10 @@
         <v>63</v>
       </c>
       <c r="AK211" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="AM211" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN211" s="1" t="s">
-        <v>1099</v>
+        <v>1069</v>
+      </c>
+      <c r="AM211" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT211" s="1" t="s">
         <v>66</v>
@@ -21955,84 +21941,11 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C212" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F212" s="1" t="str">
-        <f aca="false">IF(C212="Singapore",IF(LEN(TEXT(E212,"000000"))=6,LEFT(TEXT(E212,"000000"),2),""),"")</f>
-        <v>67</v>
-      </c>
-      <c r="H212" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I212" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J212" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="C212" s="11"/>
       <c r="K212" s="11"/>
-      <c r="L212" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="M212" s="1" t="n">
-        <v>1.378723</v>
-      </c>
-      <c r="N212" s="1" t="n">
-        <v>103.773386</v>
-      </c>
-      <c r="O212" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="P212" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R212" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH212" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI212" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK212" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="AM212" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AT212" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AU212" s="1" t="str">
-        <f aca="false">IF(OR(AT212=TRUE(),AT212="TRUE"),"This sample listing is provided solely to demonstrate the directory interface. It does not represent a live declaration, verification, endorsement or participating establishment.","")</f>
-        <v/>
-      </c>
-      <c r="AV212" s="1" t="str">
-        <f aca="false">IF(OR(A212="",B212="",C212="",D212=""),"Missing required fields",IF(NOT(AND(ISNUMBER(M212),ISNUMBER(N212))),"Missing coordinates","Complete"))</f>
-        <v>Complete</v>
-      </c>
-      <c r="AW212" s="1" t="str">
-        <f aca="false">IF(AND(ISNUMBER(M212),ISNUMBER(N212)),"Ready","Coordinates required")</f>
-        <v>Ready</v>
-      </c>
-      <c r="AX212" s="1" t="str">
-        <f aca="false">IF(OR(AT212=TRUE(),AT212="TRUE"),"Demo record",IF(A212="","Missing ID",IF(B212="","Missing name",IF(NOT(AND(ISNUMBER(M212),ISNUMBER(N212))),"Coordinates required","Ready for publication"))))</f>
-        <v>Ready for publication</v>
-      </c>
+      <c r="L212" s="11"/>
+      <c r="O212" s="11"/>
+      <c r="AM212" s="12"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C213" s="11"/>
@@ -26905,18 +26818,18 @@
         <v>9</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>194</v>
@@ -26928,12 +26841,12 @@
         <v>193</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>194</v>
@@ -26945,12 +26858,12 @@
         <v>193</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>194</v>
@@ -26962,12 +26875,12 @@
         <v>193</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>194</v>
@@ -26979,12 +26892,12 @@
         <v>193</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>194</v>
@@ -26996,12 +26909,12 @@
         <v>193</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>194</v>
@@ -27013,12 +26926,12 @@
         <v>193</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>239</v>
@@ -27030,12 +26943,12 @@
         <v>238</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>239</v>
@@ -27047,12 +26960,12 @@
         <v>238</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>389</v>
@@ -27064,12 +26977,12 @@
         <v>388</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>389</v>
@@ -27081,12 +26994,12 @@
         <v>388</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>365</v>
@@ -27098,12 +27011,12 @@
         <v>364</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>365</v>
@@ -27115,12 +27028,12 @@
         <v>364</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>365</v>
@@ -27132,12 +27045,12 @@
         <v>364</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>213</v>
@@ -27149,12 +27062,12 @@
         <v>212</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>213</v>
@@ -27166,12 +27079,12 @@
         <v>212</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>213</v>
@@ -27183,12 +27096,12 @@
         <v>212</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>602</v>
@@ -27200,12 +27113,12 @@
         <v>601</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>223</v>
@@ -27217,12 +27130,12 @@
         <v>222</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>223</v>
@@ -27234,12 +27147,12 @@
         <v>222</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>339</v>
@@ -27251,12 +27164,12 @@
         <v>338</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>339</v>
@@ -27268,46 +27181,46 @@
         <v>338</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>1131</v>
-      </c>
       <c r="E23" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>566</v>
@@ -27319,12 +27232,12 @@
         <v>565</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>566</v>
@@ -27336,12 +27249,12 @@
         <v>565</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>566</v>
@@ -27353,12 +27266,12 @@
         <v>565</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>566</v>
@@ -27367,15 +27280,15 @@
         <v>567</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>109</v>
@@ -27387,12 +27300,12 @@
         <v>108</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>109</v>
@@ -27404,12 +27317,12 @@
         <v>108</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>109</v>
@@ -27418,15 +27331,15 @@
         <v>110</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>56</v>
@@ -27435,15 +27348,15 @@
         <v>57</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>56</v>
@@ -27455,12 +27368,12 @@
         <v>55</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>56</v>
@@ -27472,12 +27385,12 @@
         <v>55</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>187</v>
@@ -27489,12 +27402,12 @@
         <v>321</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>187</v>
@@ -27506,12 +27419,12 @@
         <v>321</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>187</v>
@@ -27523,12 +27436,12 @@
         <v>186</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>187</v>
@@ -27540,12 +27453,12 @@
         <v>186</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>519</v>
@@ -27557,12 +27470,12 @@
         <v>518</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>519</v>
@@ -27574,12 +27487,12 @@
         <v>518</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>519</v>
@@ -27591,12 +27504,12 @@
         <v>518</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>519</v>
@@ -27608,12 +27521,12 @@
         <v>642</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>268</v>
@@ -27625,12 +27538,12 @@
         <v>267</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>268</v>
@@ -27642,12 +27555,12 @@
         <v>267</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>268</v>
@@ -27659,12 +27572,12 @@
         <v>267</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>268</v>
@@ -27673,15 +27586,15 @@
         <v>269</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>157</v>
@@ -27693,12 +27606,12 @@
         <v>156</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>157</v>
@@ -27710,12 +27623,12 @@
         <v>156</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>157</v>
@@ -27727,12 +27640,12 @@
         <v>156</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>165</v>
@@ -27744,12 +27657,12 @@
         <v>164</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>165</v>
@@ -27761,12 +27674,12 @@
         <v>164</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>71</v>
@@ -27778,12 +27691,12 @@
         <v>70</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>71</v>
@@ -27795,12 +27708,12 @@
         <v>70</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>492</v>
@@ -27812,12 +27725,12 @@
         <v>491</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>492</v>
@@ -27829,12 +27742,12 @@
         <v>491</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>492</v>
@@ -27843,15 +27756,15 @@
         <v>493</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>314</v>
@@ -27863,12 +27776,12 @@
         <v>313</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>314</v>
@@ -27880,12 +27793,12 @@
         <v>313</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>174</v>
@@ -27894,15 +27807,15 @@
         <v>175</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>174</v>
@@ -27914,12 +27827,12 @@
         <v>173</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>254</v>
@@ -27928,15 +27841,15 @@
         <v>255</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>254</v>
@@ -27945,15 +27858,15 @@
         <v>255</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>254</v>
@@ -27965,12 +27878,12 @@
         <v>253</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>254</v>
@@ -27982,12 +27895,12 @@
         <v>253</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>254</v>
@@ -27999,12 +27912,12 @@
         <v>253</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>88</v>
@@ -28016,12 +27929,12 @@
         <v>140</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>88</v>
@@ -28033,12 +27946,12 @@
         <v>140</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>88</v>
@@ -28050,12 +27963,12 @@
         <v>87</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>88</v>
@@ -28067,114 +27980,114 @@
         <v>87</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D70" s="14" t="s">
         <v>1187</v>
       </c>
-      <c r="B70" s="14" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>1190</v>
-      </c>
       <c r="E70" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="C71" s="14" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D71" s="14" t="s">
         <v>1189</v>
       </c>
-      <c r="D71" s="14" t="s">
-        <v>1192</v>
-      </c>
       <c r="E71" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="C72" s="14" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D72" s="14" t="s">
         <v>1189</v>
       </c>
-      <c r="D72" s="14" t="s">
-        <v>1192</v>
-      </c>
       <c r="E72" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D73" s="14" t="s">
         <v>1194</v>
       </c>
-      <c r="B73" s="14" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>1197</v>
-      </c>
       <c r="E73" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>582</v>
@@ -28186,12 +28099,12 @@
         <v>581</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>582</v>
@@ -28200,49 +28113,49 @@
         <v>583</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>831</v>
@@ -28254,12 +28167,12 @@
         <v>830</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>831</v>
@@ -28271,12 +28184,12 @@
         <v>830</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>165</v>
@@ -28288,12 +28201,12 @@
         <v>480</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>492</v>
@@ -28302,15 +28215,15 @@
         <v>493</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>254</v>
@@ -28319,10 +28232,10 @@
         <v>255</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
@@ -28364,7 +28277,7 @@
         <v>14</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>18</v>
@@ -28387,27 +28300,27 @@
         <v>59</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>1213</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>1214</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>197</v>
@@ -28419,69 +28332,69 @@
         <v>66</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>414</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>1222</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>1223</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>1224</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>1226</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="F5" s="16" t="s">
         <v>1227</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>399</v>
@@ -28492,24 +28405,24 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28525,45 +28438,45 @@
         <v>589</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -28591,42 +28504,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
   </sheetData>

--- a/data/community-listings.xlsx
+++ b/data/community-listings.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4073" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="1246">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -565,7 +565,10 @@
     <t xml:space="preserve">Al-Tasneem</t>
   </si>
   <si>
-    <t xml:space="preserve">786 North Bridge Road</t>
+    <t xml:space="preserve">709 North Bridge Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198681</t>
   </si>
   <si>
     <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2023-12-17.</t>
@@ -646,7 +649,7 @@
     <t xml:space="preserve">320090</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-04-14. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
+    <t xml:space="preserve">Reported temporarily closed (Google Maps, checked 2026-10-19); confirm before visiting. Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-04-14. Postal code from OneMap, Singapore Land Authority, under the Singapore Open Data Licence v1.0.</t>
   </si>
   <si>
     <t xml:space="preserve">com-4ffbd41c</t>
@@ -1432,10 +1435,10 @@
     <t xml:space="preserve">Hai Ge Ji Hainanese Chicken Rice</t>
   </si>
   <si>
-    <t xml:space="preserve">783 North Bridge Road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198751</t>
+    <t xml:space="preserve">70 Bussorah Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199483</t>
   </si>
   <si>
     <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-09-23.</t>
@@ -1573,10 +1576,10 @@
     <t xml:space="preserve">Imam Banana Leaf Restaurant</t>
   </si>
   <si>
-    <t xml:space="preserve">10 Lorong 1 Geylang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389119</t>
+    <t xml:space="preserve">12 Lorong 1 Geylang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389120</t>
   </si>
   <si>
     <t xml:space="preserve">Geylang</t>
@@ -1759,7 +1762,7 @@
     <t xml:space="preserve">com-da3dd50b</t>
   </si>
   <si>
-    <t xml:space="preserve">Kofu</t>
+    <t xml:space="preserve">Koufu</t>
   </si>
   <si>
     <t xml:space="preserve">511 Canberra Road #01-01</t>
@@ -1817,9 +1820,6 @@
   </si>
   <si>
     <t xml:space="preserve">com-2c871de1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koufu</t>
   </si>
   <si>
     <t xml:space="preserve">70 Stamford Road</t>
@@ -2746,7 +2746,7 @@
     <t xml:space="preserve">Pizza, Italian, Pasta, Salad</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-01-16.</t>
+    <t xml:space="preserve">Reported temporarily closed (Google Maps, checked 2026-10-19); confirm before visiting. Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-01-16.</t>
   </si>
   <si>
     <t xml:space="preserve">com-b4571b01</t>
@@ -3187,24 +3187,6 @@
     <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-10-09.</t>
   </si>
   <si>
-    <t xml:space="preserve">com-8c21c6c5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Halia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Cluny Road, Singapore Botanic Gardens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">259569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2024-10-03.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://thehalia.com/</t>
-  </si>
-  <si>
     <t xml:space="preserve">com-8b1b6e42</t>
   </si>
   <si>
@@ -3365,6 +3347,9 @@
   </si>
   <si>
     <t xml:space="preserve">Yakiniku OK!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported temporarily closed (Google Maps, checked 2026-10-19); confirm before visiting. Source: OpenStreetMap (© OpenStreetMap contributors, ODbL). OSM record last updated 2023-05-11.</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.facebook.com/yakinikuok/</t>
@@ -4287,8 +4272,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblEstablishments" displayName="tblEstablishments" ref="A1:AX211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:AX211"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblEstablishments" displayName="tblEstablishments" ref="A1:AX210" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:AX210"/>
   <tableColumns count="50">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
@@ -6395,19 +6380,22 @@
       <c r="D20" s="1" t="s">
         <v>180</v>
       </c>
+      <c r="E20" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="F20" s="1" t="str">
         <f aca="false">IF(C20="Singapore",IF(LEN(TEXT(E20,"000000"))=6,LEFT(TEXT(E20,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>19</v>
       </c>
       <c r="K20" s="11"/>
       <c r="L20" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>1.302464</v>
+        <v>1.3023797</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>103.858615</v>
+        <v>103.8586212</v>
       </c>
       <c r="O20" s="11" t="s">
         <v>60</v>
@@ -6425,7 +6413,7 @@
         <v>63</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM20" s="12" t="n">
         <v>46311</v>
@@ -6452,32 +6440,32 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F21" s="1" t="str">
         <f aca="false">IF(C21="Singapore",IF(LEN(TEXT(E21,"000000"))=6,LEFT(TEXT(E21,"000000"),2),""),"")</f>
         <v>36</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>102</v>
@@ -6507,7 +6495,7 @@
         <v>63</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM21" s="12" t="n">
         <v>46311</v>
@@ -6534,35 +6522,35 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>52</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F22" s="1" t="str">
         <f aca="false">IF(C22="Singapore",IF(LEN(TEXT(E22,"000000"))=6,LEFT(TEXT(E22,"000000"),2),""),"")</f>
         <v>03</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>1.289255</v>
@@ -6586,7 +6574,7 @@
         <v>63</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM22" s="12" t="n">
         <v>46311</v>
@@ -6613,16 +6601,16 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F23" s="1" t="str">
         <f aca="false">IF(C23="Singapore",IF(LEN(TEXT(E23,"000000"))=6,LEFT(TEXT(E23,"000000"),2),""),"")</f>
@@ -6654,7 +6642,7 @@
         <v>63</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM23" s="12" t="n">
         <v>46311</v>
@@ -6681,19 +6669,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F24" s="1" t="str">
         <f aca="false">IF(C24="Singapore",IF(LEN(TEXT(E24,"000000"))=6,LEFT(TEXT(E24,"000000"),2),""),"")</f>
@@ -6736,7 +6724,7 @@
         <v>63</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM24" s="12" t="s">
         <v>65</v>
@@ -6763,35 +6751,35 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F25" s="1" t="str">
         <f aca="false">IF(C25="Singapore",IF(LEN(TEXT(E25,"000000"))=6,LEFT(TEXT(E25,"000000"),2),""),"")</f>
         <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L25" s="11" t="s">
         <v>59</v>
@@ -6818,13 +6806,13 @@
         <v>63</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM25" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AT25" s="1" t="s">
         <v>66</v>
@@ -6848,38 +6836,38 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F26" s="1" t="str">
         <f aca="false">IF(C26="Singapore",IF(LEN(TEXT(E26,"000000"))=6,LEFT(TEXT(E26,"000000"),2),""),"")</f>
         <v>18</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>1.296024</v>
@@ -6903,13 +6891,13 @@
         <v>63</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM26" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN26" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AT26" s="1" t="s">
         <v>66</v>
@@ -6933,19 +6921,19 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F27" s="1" t="str">
         <f aca="false">IF(C27="Singapore",IF(LEN(TEXT(E27,"000000"))=6,LEFT(TEXT(E27,"000000"),2),""),"")</f>
@@ -6964,7 +6952,7 @@
         <v>90</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>1.312239</v>
@@ -6988,13 +6976,13 @@
         <v>63</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM27" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN27" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AT27" s="1" t="s">
         <v>66</v>
@@ -7018,35 +7006,35 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F28" s="1" t="str">
         <f aca="false">IF(C28="Singapore",IF(LEN(TEXT(E28,"000000"))=6,LEFT(TEXT(E28,"000000"),2),""),"")</f>
         <v>07</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L28" s="11" t="s">
         <v>59</v>
@@ -7073,7 +7061,7 @@
         <v>63</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM28" s="12" t="n">
         <v>46311</v>
@@ -7100,19 +7088,19 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F29" s="1" t="str">
         <f aca="false">IF(C29="Singapore",IF(LEN(TEXT(E29,"000000"))=6,LEFT(TEXT(E29,"000000"),2),""),"")</f>
@@ -7129,7 +7117,7 @@
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>1.341239</v>
@@ -7153,7 +7141,7 @@
         <v>63</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AM29" s="12" t="n">
         <v>46311</v>
@@ -7180,32 +7168,32 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F30" s="1" t="str">
         <f aca="false">IF(C30="Singapore",IF(LEN(TEXT(E30,"000000"))=6,LEFT(TEXT(E30,"000000"),2),""),"")</f>
         <v>63</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>102</v>
@@ -7235,7 +7223,7 @@
         <v>63</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM30" s="12" t="n">
         <v>46311</v>
@@ -7262,19 +7250,19 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F31" s="1" t="str">
         <f aca="false">IF(C31="Singapore",IF(LEN(TEXT(E31,"000000"))=6,LEFT(TEXT(E31,"000000"),2),""),"")</f>
@@ -7290,7 +7278,7 @@
         <v>72</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>59</v>
@@ -7317,7 +7305,7 @@
         <v>63</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM31" s="12" t="s">
         <v>65</v>
@@ -7344,32 +7332,32 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F32" s="1" t="str">
         <f aca="false">IF(C32="Singapore",IF(LEN(TEXT(E32,"000000"))=6,LEFT(TEXT(E32,"000000"),2),""),"")</f>
         <v>42</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="11" t="s">
@@ -7397,13 +7385,13 @@
         <v>63</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM32" s="12" t="s">
         <v>65</v>
       </c>
       <c r="AN32" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AT32" s="1" t="s">
         <v>66</v>
@@ -7427,19 +7415,19 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F33" s="1" t="str">
         <f aca="false">IF(C33="Singapore",IF(LEN(TEXT(E33,"000000"))=6,LEFT(TEXT(E33,"000000"),2),""),"")</f>
@@ -7455,7 +7443,7 @@
         <v>57</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L33" s="11" t="s">
         <v>59</v>
@@ -7509,23 +7497,23 @@
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F34" s="1" t="str">
         <f aca="false">IF(C34="Singapore",IF(LEN(TEXT(E34,"000000"))=6,LEFT(TEXT(E34,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L34" s="11" t="s">
         <v>59</v>
@@ -7552,7 +7540,7 @@
         <v>63</v>
       </c>
       <c r="AK34" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM34" s="12" t="n">
         <v>46311</v>
@@ -7579,35 +7567,35 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F35" s="1" t="str">
         <f aca="false">IF(C35="Singapore",IF(LEN(TEXT(E35,"000000"))=6,LEFT(TEXT(E35,"000000"),2),""),"")</f>
         <v>05</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L35" s="11" t="s">
         <v>59</v>
@@ -7634,13 +7622,13 @@
         <v>63</v>
       </c>
       <c r="AK35" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM35" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN35" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AT35" s="1" t="s">
         <v>66</v>
@@ -7664,32 +7652,32 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F36" s="1" t="str">
         <f aca="false">IF(C36="Singapore",IF(LEN(TEXT(E36,"000000"))=6,LEFT(TEXT(E36,"000000"),2),""),"")</f>
         <v>19</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>102</v>
@@ -7719,7 +7707,7 @@
         <v>63</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM36" s="12" t="n">
         <v>46311</v>
@@ -7746,19 +7734,19 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F37" s="1" t="str">
         <f aca="false">IF(C37="Singapore",IF(LEN(TEXT(E37,"000000"))=6,LEFT(TEXT(E37,"000000"),2),""),"")</f>
@@ -7774,7 +7762,7 @@
         <v>57</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L37" s="11" t="s">
         <v>59</v>
@@ -7801,7 +7789,7 @@
         <v>63</v>
       </c>
       <c r="AK37" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM37" s="12" t="s">
         <v>65</v>
@@ -7828,19 +7816,19 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F38" s="1" t="str">
         <f aca="false">IF(C38="Singapore",IF(LEN(TEXT(E38,"000000"))=6,LEFT(TEXT(E38,"000000"),2),""),"")</f>
@@ -7856,7 +7844,7 @@
         <v>166</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L38" s="11" t="s">
         <v>59</v>
@@ -7883,7 +7871,7 @@
         <v>63</v>
       </c>
       <c r="AK38" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM38" s="12" t="n">
         <v>46311</v>
@@ -7910,10 +7898,10 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>52</v>
@@ -7969,7 +7957,7 @@
         <v>46311</v>
       </c>
       <c r="AN39" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AT39" s="1" t="s">
         <v>66</v>
@@ -7993,19 +7981,19 @@
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F40" s="1" t="str">
         <f aca="false">IF(C40="Singapore",IF(LEN(TEXT(E40,"000000"))=6,LEFT(TEXT(E40,"000000"),2),""),"")</f>
@@ -8046,7 +8034,7 @@
         <v>63</v>
       </c>
       <c r="AK40" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM40" s="12" t="n">
         <v>46311</v>
@@ -8073,32 +8061,32 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F41" s="1" t="str">
         <f aca="false">IF(C41="Singapore",IF(LEN(TEXT(E41,"000000"))=6,LEFT(TEXT(E41,"000000"),2),""),"")</f>
         <v>57</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>102</v>
@@ -8128,13 +8116,13 @@
         <v>63</v>
       </c>
       <c r="AK41" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM41" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN41" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AT41" s="1" t="s">
         <v>66</v>
@@ -8158,32 +8146,32 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F42" s="1" t="str">
         <f aca="false">IF(C42="Singapore",IF(LEN(TEXT(E42,"000000"))=6,LEFT(TEXT(E42,"000000"),2),""),"")</f>
         <v>34</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>102</v>
@@ -8213,13 +8201,13 @@
         <v>63</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM42" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN42" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AT42" s="1" t="s">
         <v>66</v>
@@ -8243,19 +8231,19 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F43" s="1" t="str">
         <f aca="false">IF(C43="Singapore",IF(LEN(TEXT(E43,"000000"))=6,LEFT(TEXT(E43,"000000"),2),""),"")</f>
@@ -8271,7 +8259,7 @@
         <v>158</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L43" s="11" t="s">
         <v>59</v>
@@ -8298,13 +8286,13 @@
         <v>63</v>
       </c>
       <c r="AK43" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM43" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN43" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AT43" s="1" t="s">
         <v>66</v>
@@ -8328,16 +8316,16 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F44" s="1" t="str">
         <f aca="false">IF(C44="Singapore",IF(LEN(TEXT(E44,"000000"))=6,LEFT(TEXT(E44,"000000"),2),""),"")</f>
@@ -8396,35 +8384,35 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F45" s="1" t="str">
         <f aca="false">IF(C45="Singapore",IF(LEN(TEXT(E45,"000000"))=6,LEFT(TEXT(E45,"000000"),2),""),"")</f>
         <v>20</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L45" s="11" t="s">
         <v>59</v>
@@ -8451,13 +8439,13 @@
         <v>63</v>
       </c>
       <c r="AK45" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM45" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN45" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT45" s="1" t="s">
         <v>66</v>
@@ -8481,10 +8469,10 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>52</v>
@@ -8542,7 +8530,7 @@
         <v>46311</v>
       </c>
       <c r="AN46" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AT46" s="1" t="s">
         <v>66</v>
@@ -8566,19 +8554,19 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F47" s="1" t="str">
         <f aca="false">IF(C47="Singapore",IF(LEN(TEXT(E47,"000000"))=6,LEFT(TEXT(E47,"000000"),2),""),"")</f>
@@ -8594,7 +8582,7 @@
         <v>72</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L47" s="11" t="s">
         <v>59</v>
@@ -8627,7 +8615,7 @@
         <v>46311</v>
       </c>
       <c r="AN47" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AT47" s="1" t="s">
         <v>66</v>
@@ -8651,10 +8639,10 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>52</v>
@@ -8679,7 +8667,7 @@
         <v>72</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L48" s="11" t="s">
         <v>59</v>
@@ -8733,32 +8721,32 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F49" s="1" t="str">
         <f aca="false">IF(C49="Singapore",IF(LEN(TEXT(E49,"000000"))=6,LEFT(TEXT(E49,"000000"),2),""),"")</f>
         <v>18</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>90</v>
@@ -8788,7 +8776,7 @@
         <v>63</v>
       </c>
       <c r="AK49" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM49" s="12" t="s">
         <v>65</v>
@@ -8815,32 +8803,32 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F50" s="1" t="str">
         <f aca="false">IF(C50="Singapore",IF(LEN(TEXT(E50,"000000"))=6,LEFT(TEXT(E50,"000000"),2),""),"")</f>
         <v>12</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="11" t="s">
@@ -8868,7 +8856,7 @@
         <v>63</v>
       </c>
       <c r="AK50" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM50" s="12" t="s">
         <v>65</v>
@@ -8895,19 +8883,19 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F51" s="1" t="str">
         <f aca="false">IF(C51="Singapore",IF(LEN(TEXT(E51,"000000"))=6,LEFT(TEXT(E51,"000000"),2),""),"")</f>
@@ -8948,13 +8936,13 @@
         <v>63</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM51" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN51" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AT51" s="1" t="s">
         <v>66</v>
@@ -8978,19 +8966,19 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F52" s="1" t="str">
         <f aca="false">IF(C52="Singapore",IF(LEN(TEXT(E52,"000000"))=6,LEFT(TEXT(E52,"000000"),2),""),"")</f>
@@ -9006,7 +8994,7 @@
         <v>57</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L52" s="11" t="s">
         <v>112</v>
@@ -9033,13 +9021,13 @@
         <v>63</v>
       </c>
       <c r="AK52" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM52" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN52" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AT52" s="1" t="s">
         <v>66</v>
@@ -9063,16 +9051,16 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>163</v>
@@ -9145,35 +9133,35 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F54" s="1" t="str">
         <f aca="false">IF(C54="Singapore",IF(LEN(TEXT(E54,"000000"))=6,LEFT(TEXT(E54,"000000"),2),""),"")</f>
         <v>10</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L54" s="11" t="s">
         <v>59</v>
@@ -9200,13 +9188,13 @@
         <v>63</v>
       </c>
       <c r="AK54" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM54" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN54" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AT54" s="1" t="s">
         <v>66</v>
@@ -9230,35 +9218,35 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F55" s="1" t="str">
         <f aca="false">IF(C55="Singapore",IF(LEN(TEXT(E55,"000000"))=6,LEFT(TEXT(E55,"000000"),2),""),"")</f>
         <v>34</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L55" s="11" t="s">
         <v>59</v>
@@ -9285,13 +9273,13 @@
         <v>63</v>
       </c>
       <c r="AK55" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM55" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN55" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AT55" s="1" t="s">
         <v>66</v>
@@ -9315,10 +9303,10 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>52</v>
@@ -9343,7 +9331,7 @@
         <v>72</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L56" s="11" t="s">
         <v>59</v>
@@ -9370,13 +9358,13 @@
         <v>63</v>
       </c>
       <c r="AK56" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM56" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN56" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AT56" s="1" t="s">
         <v>66</v>
@@ -9400,10 +9388,10 @@
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>52</v>
@@ -9428,7 +9416,7 @@
         <v>72</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L57" s="11" t="s">
         <v>59</v>
@@ -9461,7 +9449,7 @@
         <v>46311</v>
       </c>
       <c r="AN57" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AT57" s="1" t="s">
         <v>66</v>
@@ -9485,16 +9473,16 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F58" s="1" t="str">
         <f aca="false">IF(C58="Singapore",IF(LEN(TEXT(E58,"000000"))=6,LEFT(TEXT(E58,"000000"),2),""),"")</f>
@@ -9502,7 +9490,7 @@
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>1.354264</v>
@@ -9553,10 +9541,10 @@
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>52</v>
@@ -9612,7 +9600,7 @@
         <v>46311</v>
       </c>
       <c r="AN59" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AT59" s="1" t="s">
         <v>66</v>
@@ -9636,10 +9624,10 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>52</v>
@@ -9664,7 +9652,7 @@
         <v>72</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L60" s="11" t="s">
         <v>59</v>
@@ -9691,7 +9679,7 @@
         <v>63</v>
       </c>
       <c r="AK60" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM60" s="12" t="n">
         <v>46311</v>
@@ -9718,19 +9706,19 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F61" s="1" t="str">
         <f aca="false">IF(C61="Singapore",IF(LEN(TEXT(E61,"000000"))=6,LEFT(TEXT(E61,"000000"),2),""),"")</f>
@@ -9746,7 +9734,7 @@
         <v>72</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L61" s="11" t="s">
         <v>59</v>
@@ -9773,13 +9761,13 @@
         <v>63</v>
       </c>
       <c r="AK61" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM61" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN61" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AT61" s="1" t="s">
         <v>66</v>
@@ -9803,19 +9791,19 @@
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F62" s="1" t="str">
         <f aca="false">IF(C62="Singapore",IF(LEN(TEXT(E62,"000000"))=6,LEFT(TEXT(E62,"000000"),2),""),"")</f>
@@ -9831,7 +9819,7 @@
         <v>89</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L62" s="11" t="s">
         <v>59</v>
@@ -9858,13 +9846,13 @@
         <v>63</v>
       </c>
       <c r="AK62" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM62" s="12" t="s">
         <v>65</v>
       </c>
       <c r="AN62" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AT62" s="1" t="s">
         <v>66</v>
@@ -9888,23 +9876,23 @@
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F63" s="1" t="str">
         <f aca="false">IF(C63="Singapore",IF(LEN(TEXT(E63,"000000"))=6,LEFT(TEXT(E63,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L63" s="11" t="s">
         <v>59</v>
@@ -9931,7 +9919,7 @@
         <v>63</v>
       </c>
       <c r="AK63" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM63" s="12" t="n">
         <v>46311</v>
@@ -9958,16 +9946,16 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F64" s="1" t="str">
         <f aca="false">IF(C64="Singapore",IF(LEN(TEXT(E64,"000000"))=6,LEFT(TEXT(E64,"000000"),2),""),"")</f>
@@ -9999,7 +9987,7 @@
         <v>63</v>
       </c>
       <c r="AK64" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM64" s="12" t="n">
         <v>46311</v>
@@ -10026,19 +10014,19 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F65" s="1" t="str">
         <f aca="false">IF(C65="Singapore",IF(LEN(TEXT(E65,"000000"))=6,LEFT(TEXT(E65,"000000"),2),""),"")</f>
@@ -10054,7 +10042,7 @@
         <v>57</v>
       </c>
       <c r="K65" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L65" s="11" t="s">
         <v>112</v>
@@ -10081,7 +10069,7 @@
         <v>63</v>
       </c>
       <c r="AK65" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM65" s="12" t="s">
         <v>65</v>
@@ -10108,19 +10096,19 @@
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F66" s="1" t="str">
         <f aca="false">IF(C66="Singapore",IF(LEN(TEXT(E66,"000000"))=6,LEFT(TEXT(E66,"000000"),2),""),"")</f>
@@ -10136,7 +10124,7 @@
         <v>89</v>
       </c>
       <c r="K66" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L66" s="11" t="s">
         <v>112</v>
@@ -10163,7 +10151,7 @@
         <v>63</v>
       </c>
       <c r="AK66" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM66" s="12" t="s">
         <v>65</v>
@@ -10190,23 +10178,23 @@
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F67" s="1" t="str">
         <f aca="false">IF(C67="Singapore",IF(LEN(TEXT(E67,"000000"))=6,LEFT(TEXT(E67,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L67" s="11" t="s">
         <v>112</v>
@@ -10233,7 +10221,7 @@
         <v>63</v>
       </c>
       <c r="AK67" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM67" s="12" t="n">
         <v>46311</v>
@@ -10260,10 +10248,10 @@
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>52</v>
@@ -10289,7 +10277,7 @@
       </c>
       <c r="K68" s="11"/>
       <c r="L68" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M68" s="1" t="n">
         <v>1.372372</v>
@@ -10313,13 +10301,13 @@
         <v>63</v>
       </c>
       <c r="AK68" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM68" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN68" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AT68" s="1" t="s">
         <v>66</v>
@@ -10343,19 +10331,19 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F69" s="1" t="str">
         <f aca="false">IF(C69="Singapore",IF(LEN(TEXT(E69,"000000"))=6,LEFT(TEXT(E69,"000000"),2),""),"")</f>
@@ -10371,7 +10359,7 @@
         <v>158</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L69" s="11" t="s">
         <v>59</v>
@@ -10398,7 +10386,7 @@
         <v>63</v>
       </c>
       <c r="AK69" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM69" s="12" t="n">
         <v>46311</v>
@@ -10425,16 +10413,16 @@
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F70" s="1" t="str">
         <f aca="false">IF(C70="Singapore",IF(LEN(TEXT(E70,"000000"))=6,LEFT(TEXT(E70,"000000"),2),""),"")</f>
@@ -10493,42 +10481,42 @@
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F71" s="1" t="str">
         <f aca="false">IF(C71="Singapore",IF(LEN(TEXT(E71,"000000"))=6,LEFT(TEXT(E71,"000000"),2),""),"")</f>
         <v>19</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K71" s="11"/>
       <c r="L71" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>1.303825</v>
+        <v>1.3008912</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>103.859899</v>
+        <v>103.860025</v>
       </c>
       <c r="O71" s="11" t="s">
         <v>60</v>
@@ -10546,7 +10534,7 @@
         <v>63</v>
       </c>
       <c r="AK71" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM71" s="12" t="n">
         <v>46311</v>
@@ -10573,32 +10561,32 @@
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F72" s="1" t="str">
         <f aca="false">IF(C72="Singapore",IF(LEN(TEXT(E72,"000000"))=6,LEFT(TEXT(E72,"000000"),2),""),"")</f>
         <v>43</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K72" s="11"/>
       <c r="L72" s="11" t="s">
@@ -10653,26 +10641,26 @@
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F73" s="1" t="str">
         <f aca="false">IF(C73="Singapore",IF(LEN(TEXT(E73,"000000"))=6,LEFT(TEXT(E73,"000000"),2),""),"")</f>
         <v>81</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>165</v>
@@ -10681,10 +10669,10 @@
         <v>166</v>
       </c>
       <c r="K73" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L73" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M73" s="1" t="n">
         <v>1.361812</v>
@@ -10708,7 +10696,7 @@
         <v>63</v>
       </c>
       <c r="AK73" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM73" s="12" t="s">
         <v>65</v>
@@ -10735,19 +10723,19 @@
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F74" s="1" t="str">
         <f aca="false">IF(C74="Singapore",IF(LEN(TEXT(E74,"000000"))=6,LEFT(TEXT(E74,"000000"),2),""),"")</f>
@@ -10763,7 +10751,7 @@
         <v>72</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L74" s="11" t="s">
         <v>59</v>
@@ -10790,13 +10778,13 @@
         <v>63</v>
       </c>
       <c r="AK74" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM74" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN74" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AT74" s="1" t="s">
         <v>66</v>
@@ -10820,35 +10808,35 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F75" s="1" t="str">
         <f aca="false">IF(C75="Singapore",IF(LEN(TEXT(E75,"000000"))=6,LEFT(TEXT(E75,"000000"),2),""),"")</f>
         <v>53</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K75" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L75" s="11" t="s">
         <v>59</v>
@@ -10875,13 +10863,13 @@
         <v>63</v>
       </c>
       <c r="AK75" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM75" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN75" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AT75" s="1" t="s">
         <v>66</v>
@@ -10905,38 +10893,38 @@
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F76" s="1" t="str">
         <f aca="false">IF(C76="Singapore",IF(LEN(TEXT(E76,"000000"))=6,LEFT(TEXT(E76,"000000"),2),""),"")</f>
         <v>21</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K76" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M76" s="1" t="n">
         <v>1.316628</v>
@@ -10960,7 +10948,7 @@
         <v>63</v>
       </c>
       <c r="AK76" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM76" s="12" t="n">
         <v>46311</v>
@@ -10987,19 +10975,19 @@
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F77" s="1" t="str">
         <f aca="false">IF(C77="Singapore",IF(LEN(TEXT(E77,"000000"))=6,LEFT(TEXT(E77,"000000"),2),""),"")</f>
@@ -11040,7 +11028,7 @@
         <v>63</v>
       </c>
       <c r="AK77" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM77" s="12" t="s">
         <v>65</v>
@@ -11067,10 +11055,10 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>52</v>
@@ -11095,7 +11083,7 @@
         <v>72</v>
       </c>
       <c r="K78" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L78" s="11" t="s">
         <v>59</v>
@@ -11128,7 +11116,7 @@
         <v>46311</v>
       </c>
       <c r="AN78" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AT78" s="1" t="s">
         <v>66</v>
@@ -11152,26 +11140,26 @@
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F79" s="1" t="str">
         <f aca="false">IF(C79="Singapore",IF(LEN(TEXT(E79,"000000"))=6,LEFT(TEXT(E79,"000000"),2),""),"")</f>
         <v>81</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>165</v>
@@ -11180,7 +11168,7 @@
         <v>166</v>
       </c>
       <c r="K79" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L79" s="11" t="s">
         <v>59</v>
@@ -11207,7 +11195,7 @@
         <v>63</v>
       </c>
       <c r="AK79" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM79" s="12" t="s">
         <v>65</v>
@@ -11234,44 +11222,44 @@
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F80" s="1" t="str">
         <f aca="false">IF(C80="Singapore",IF(LEN(TEXT(E80,"000000"))=6,LEFT(TEXT(E80,"000000"),2),""),"")</f>
         <v>38</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K80" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L80" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M80" s="1" t="n">
-        <v>1.311058</v>
+        <v>1.3110978</v>
       </c>
       <c r="N80" s="1" t="n">
-        <v>103.872556</v>
+        <v>103.8725542</v>
       </c>
       <c r="O80" s="11" t="s">
         <v>60</v>
@@ -11289,7 +11277,7 @@
         <v>63</v>
       </c>
       <c r="AK80" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM80" s="12" t="n">
         <v>46311</v>
@@ -11316,19 +11304,19 @@
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F81" s="1" t="str">
         <f aca="false">IF(C81="Singapore",IF(LEN(TEXT(E81,"000000"))=6,LEFT(TEXT(E81,"000000"),2),""),"")</f>
@@ -11344,7 +11332,7 @@
         <v>89</v>
       </c>
       <c r="K81" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L81" s="11" t="s">
         <v>59</v>
@@ -11371,13 +11359,13 @@
         <v>63</v>
       </c>
       <c r="AK81" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AM81" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN81" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AT81" s="1" t="s">
         <v>66</v>
@@ -11401,10 +11389,10 @@
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>52</v>
@@ -11429,7 +11417,7 @@
         <v>72</v>
       </c>
       <c r="K82" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L82" s="11" t="s">
         <v>59</v>
@@ -11483,23 +11471,23 @@
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F83" s="1" t="str">
         <f aca="false">IF(C83="Singapore",IF(LEN(TEXT(E83,"000000"))=6,LEFT(TEXT(E83,"000000"),2),""),"")</f>
         <v>00</v>
       </c>
       <c r="K83" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L83" s="11" t="s">
         <v>59</v>
@@ -11526,7 +11514,7 @@
         <v>63</v>
       </c>
       <c r="AK83" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM83" s="12" t="n">
         <v>46311</v>
@@ -11553,35 +11541,35 @@
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F84" s="1" t="str">
         <f aca="false">IF(C84="Singapore",IF(LEN(TEXT(E84,"000000"))=6,LEFT(TEXT(E84,"000000"),2),""),"")</f>
         <v>42</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K84" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L84" s="11" t="s">
         <v>59</v>
@@ -11608,13 +11596,13 @@
         <v>63</v>
       </c>
       <c r="AK84" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM84" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN84" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AT84" s="1" t="s">
         <v>66</v>
@@ -11638,35 +11626,35 @@
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F85" s="1" t="str">
         <f aca="false">IF(C85="Singapore",IF(LEN(TEXT(E85,"000000"))=6,LEFT(TEXT(E85,"000000"),2),""),"")</f>
         <v>36</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K85" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L85" s="11" t="s">
         <v>59</v>
@@ -11693,7 +11681,7 @@
         <v>63</v>
       </c>
       <c r="AK85" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM85" s="12" t="n">
         <v>46311</v>
@@ -11720,19 +11708,19 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F86" s="1" t="str">
         <f aca="false">IF(C86="Singapore",IF(LEN(TEXT(E86,"000000"))=6,LEFT(TEXT(E86,"000000"),2),""),"")</f>
@@ -11748,7 +11736,7 @@
         <v>158</v>
       </c>
       <c r="K86" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L86" s="11" t="s">
         <v>59</v>
@@ -11775,13 +11763,13 @@
         <v>63</v>
       </c>
       <c r="AK86" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM86" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN86" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AT86" s="1" t="s">
         <v>66</v>
@@ -11805,32 +11793,32 @@
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F87" s="1" t="str">
         <f aca="false">IF(C87="Singapore",IF(LEN(TEXT(E87,"000000"))=6,LEFT(TEXT(E87,"000000"),2),""),"")</f>
         <v>12</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K87" s="11"/>
       <c r="L87" s="11" t="s">
@@ -11858,7 +11846,7 @@
         <v>63</v>
       </c>
       <c r="AK87" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM87" s="12" t="n">
         <v>46311</v>
@@ -11885,32 +11873,32 @@
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F88" s="1" t="str">
         <f aca="false">IF(C88="Singapore",IF(LEN(TEXT(E88,"000000"))=6,LEFT(TEXT(E88,"000000"),2),""),"")</f>
         <v>63</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K88" s="11" t="s">
         <v>58</v>
@@ -11940,7 +11928,7 @@
         <v>63</v>
       </c>
       <c r="AK88" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM88" s="12" t="n">
         <v>46311</v>
@@ -11967,32 +11955,32 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F89" s="1" t="str">
         <f aca="false">IF(C89="Singapore",IF(LEN(TEXT(E89,"000000"))=6,LEFT(TEXT(E89,"000000"),2),""),"")</f>
         <v>26</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K89" s="11" t="s">
         <v>58</v>
@@ -12022,13 +12010,13 @@
         <v>63</v>
       </c>
       <c r="AK89" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM89" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN89" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AT89" s="1" t="s">
         <v>66</v>
@@ -12052,10 +12040,10 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>52</v>
@@ -12122,32 +12110,32 @@
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F91" s="1" t="str">
         <f aca="false">IF(C91="Singapore",IF(LEN(TEXT(E91,"000000"))=6,LEFT(TEXT(E91,"000000"),2),""),"")</f>
         <v>57</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K91" s="11"/>
       <c r="L91" s="11" t="s">
@@ -12175,7 +12163,7 @@
         <v>63</v>
       </c>
       <c r="AK91" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM91" s="12" t="s">
         <v>65</v>
@@ -12202,19 +12190,19 @@
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="1" t="str">
         <f aca="false">IF(C92="Singapore",IF(LEN(TEXT(E92,"000000"))=6,LEFT(TEXT(E92,"000000"),2),""),"")</f>
@@ -12257,7 +12245,7 @@
         <v>63</v>
       </c>
       <c r="AK92" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM92" s="12" t="n">
         <v>46311</v>
@@ -12284,35 +12272,35 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F93" s="1" t="str">
         <f aca="false">IF(C93="Singapore",IF(LEN(TEXT(E93,"000000"))=6,LEFT(TEXT(E93,"000000"),2),""),"")</f>
         <v>75</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="K93" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L93" s="11" t="s">
         <v>59</v>
@@ -12339,7 +12327,7 @@
         <v>63</v>
       </c>
       <c r="AK93" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM93" s="12" t="n">
         <v>46311</v>
@@ -12366,35 +12354,35 @@
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F94" s="1" t="str">
         <f aca="false">IF(C94="Singapore",IF(LEN(TEXT(E94,"000000"))=6,LEFT(TEXT(E94,"000000"),2),""),"")</f>
         <v>19</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K94" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L94" s="11" t="s">
         <v>59</v>
@@ -12421,7 +12409,7 @@
         <v>63</v>
       </c>
       <c r="AK94" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM94" s="12" t="s">
         <v>65</v>
@@ -12448,36 +12436,36 @@
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F95" s="1" t="str">
         <f aca="false">IF(C95="Singapore",IF(LEN(TEXT(E95,"000000"))=6,LEFT(TEXT(E95,"000000"),2),""),"")</f>
         <v>19</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K95" s="11"/>
       <c r="L95" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M95" s="1" t="n">
         <v>1.301759</v>
@@ -12501,13 +12489,13 @@
         <v>63</v>
       </c>
       <c r="AK95" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM95" s="12" t="s">
         <v>65</v>
       </c>
       <c r="AN95" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AT95" s="1" t="s">
         <v>66</v>
@@ -12531,10 +12519,10 @@
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>52</v>
@@ -12630,13 +12618,13 @@
         <v>18</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K97" s="11" t="s">
         <v>609</v>
@@ -12715,13 +12703,13 @@
         <v>19</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K98" s="11" t="s">
         <v>616</v>
@@ -12809,7 +12797,7 @@
         <v>72</v>
       </c>
       <c r="K99" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L99" s="11" t="s">
         <v>59</v>
@@ -13123,19 +13111,19 @@
         <v>19</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K103" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L103" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M103" s="1" t="n">
         <v>1.302335</v>
@@ -13208,13 +13196,13 @@
         <v>642</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K104" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L104" s="11" t="s">
         <v>59</v>
@@ -13241,7 +13229,7 @@
         <v>63</v>
       </c>
       <c r="AK104" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM104" s="12" t="n">
         <v>46311</v>
@@ -13280,20 +13268,20 @@
         <v>645</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F105" s="1" t="str">
         <f aca="false">IF(C105="Singapore",IF(LEN(TEXT(E105,"000000"))=6,LEFT(TEXT(E105,"000000"),2),""),"")</f>
         <v>03</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K105" s="11" t="s">
         <v>646</v>
@@ -13454,16 +13442,16 @@
         <v>12</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K107" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L107" s="11" t="s">
         <v>59</v>
@@ -13529,26 +13517,26 @@
         <v>52</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F108" s="1" t="str">
         <f aca="false">IF(C108="Singapore",IF(LEN(TEXT(E108,"000000"))=6,LEFT(TEXT(E108,"000000"),2),""),"")</f>
         <v>34</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K108" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L108" s="11" t="s">
         <v>59</v>
@@ -13575,7 +13563,7 @@
         <v>63</v>
       </c>
       <c r="AK108" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM108" s="12" t="n">
         <v>46311</v>
@@ -13704,13 +13692,13 @@
         <v>44</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K110" s="11"/>
       <c r="L110" s="11" t="s">
@@ -13784,13 +13772,13 @@
         <v>09</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K111" s="11" t="s">
         <v>673</v>
@@ -13863,7 +13851,7 @@
         <v>00</v>
       </c>
       <c r="K112" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L112" s="11" t="s">
         <v>59</v>
@@ -13936,16 +13924,16 @@
         <v>75</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="K113" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L113" s="11" t="s">
         <v>59</v>
@@ -14018,7 +14006,7 @@
         <v>00</v>
       </c>
       <c r="K114" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L114" s="11" t="s">
         <v>59</v>
@@ -14081,26 +14069,26 @@
         <v>52</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F115" s="1" t="str">
         <f aca="false">IF(C115="Singapore",IF(LEN(TEXT(E115,"000000"))=6,LEFT(TEXT(E115,"000000"),2),""),"")</f>
         <v>63</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K115" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L115" s="11" t="s">
         <v>59</v>
@@ -14127,7 +14115,7 @@
         <v>63</v>
       </c>
       <c r="AK115" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM115" s="12" t="n">
         <v>46311</v>
@@ -14166,7 +14154,7 @@
         <v>689</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F116" s="1" t="str">
         <f aca="false">IF(C116="Singapore",IF(LEN(TEXT(E116,"000000"))=6,LEFT(TEXT(E116,"000000"),2),""),"")</f>
@@ -14182,7 +14170,7 @@
         <v>72</v>
       </c>
       <c r="K116" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L116" s="11" t="s">
         <v>59</v>
@@ -14258,16 +14246,16 @@
         <v>35</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K117" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L117" s="11" t="s">
         <v>59</v>
@@ -14330,10 +14318,10 @@
         <v>52</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F118" s="1" t="str">
         <f aca="false">IF(C118="Singapore",IF(LEN(TEXT(E118,"000000"))=6,LEFT(TEXT(E118,"000000"),2),""),"")</f>
@@ -14349,7 +14337,7 @@
         <v>57</v>
       </c>
       <c r="K118" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L118" s="11" t="s">
         <v>59</v>
@@ -14431,7 +14419,7 @@
         <v>72</v>
       </c>
       <c r="K119" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L119" s="11" t="s">
         <v>59</v>
@@ -14458,7 +14446,7 @@
         <v>63</v>
       </c>
       <c r="AK119" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM119" s="12" t="n">
         <v>46311</v>
@@ -14516,7 +14504,7 @@
         <v>89</v>
       </c>
       <c r="K120" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L120" s="11" t="s">
         <v>59</v>
@@ -14598,7 +14586,7 @@
         <v>72</v>
       </c>
       <c r="K121" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L121" s="11" t="s">
         <v>59</v>
@@ -14674,13 +14662,13 @@
         <v>34</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K122" s="11" t="s">
         <v>129</v>
@@ -14710,7 +14698,7 @@
         <v>63</v>
       </c>
       <c r="AK122" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM122" s="12" t="n">
         <v>46311</v>
@@ -14753,7 +14741,7 @@
         <v>00</v>
       </c>
       <c r="K123" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L123" s="11" t="s">
         <v>59</v>
@@ -14780,7 +14768,7 @@
         <v>63</v>
       </c>
       <c r="AK123" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM123" s="12" t="n">
         <v>46311</v>
@@ -14909,17 +14897,17 @@
         <v>12</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K125" s="11"/>
       <c r="L125" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M125" s="1" t="n">
         <v>1.315068</v>
@@ -15141,13 +15129,13 @@
         <v>06</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K128" s="11" t="s">
         <v>728</v>
@@ -15306,7 +15294,7 @@
       </c>
       <c r="K130" s="11"/>
       <c r="L130" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M130" s="1" t="n">
         <v>1.38716</v>
@@ -15376,13 +15364,13 @@
         <v>11</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K131" s="11" t="s">
         <v>123</v>
@@ -15455,7 +15443,7 @@
         <v>00</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L132" s="11" t="s">
         <v>59</v>
@@ -15528,13 +15516,13 @@
         <v>19</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K133" s="11" t="s">
         <v>102</v>
@@ -15603,20 +15591,20 @@
         <v>755</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F134" s="1" t="str">
         <f aca="false">IF(C134="Singapore",IF(LEN(TEXT(E134,"000000"))=6,LEFT(TEXT(E134,"000000"),2),""),"")</f>
         <v>43</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K134" s="11" t="s">
         <v>756</v>
@@ -15774,13 +15762,13 @@
         <v>11</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K136" s="11" t="s">
         <v>767</v>
@@ -15856,13 +15844,13 @@
         <v>34</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K137" s="11" t="s">
         <v>773</v>
@@ -15892,7 +15880,7 @@
         <v>63</v>
       </c>
       <c r="AK137" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM137" s="12" t="n">
         <v>46311</v>
@@ -16026,17 +16014,17 @@
         <v>19</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K139" s="11"/>
       <c r="L139" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M139" s="1" t="n">
         <v>1.303399</v>
@@ -16109,13 +16097,13 @@
         <v>19</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K140" s="11" t="s">
         <v>786</v>
@@ -16276,17 +16264,17 @@
         <v>19</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K142" s="11"/>
       <c r="L142" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M142" s="1" t="n">
         <v>1.302688</v>
@@ -16365,7 +16353,7 @@
         <v>72</v>
       </c>
       <c r="K143" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L143" s="11" t="s">
         <v>59</v>
@@ -16435,13 +16423,13 @@
         <v>18</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K144" s="11" t="s">
         <v>803</v>
@@ -16520,16 +16508,16 @@
         <v>34</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K145" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L145" s="11" t="s">
         <v>59</v>
@@ -16690,16 +16678,16 @@
         <v>18</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K147" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L147" s="11" t="s">
         <v>59</v>
@@ -16726,7 +16714,7 @@
         <v>63</v>
       </c>
       <c r="AK147" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM147" s="12" t="s">
         <v>65</v>
@@ -16772,13 +16760,13 @@
         <v>20</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K148" s="11" t="s">
         <v>90</v>
@@ -17025,7 +17013,7 @@
       </c>
       <c r="K151" s="11"/>
       <c r="L151" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M151" s="1" t="n">
         <v>1.429343</v>
@@ -17274,7 +17262,7 @@
         <v>89</v>
       </c>
       <c r="K154" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L154" s="11" t="s">
         <v>59</v>
@@ -17372,7 +17360,7 @@
         <v>63</v>
       </c>
       <c r="AK155" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM155" s="12" t="n">
         <v>46311</v>
@@ -17418,16 +17406,16 @@
         <v>42</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K156" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L156" s="11" t="s">
         <v>59</v>
@@ -17500,16 +17488,16 @@
         <v>19</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K157" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L157" s="11" t="s">
         <v>59</v>
@@ -17585,16 +17573,16 @@
         <v>19</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K158" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L158" s="11" t="s">
         <v>59</v>
@@ -17660,10 +17648,10 @@
         <v>52</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F159" s="1" t="str">
         <f aca="false">IF(C159="Singapore",IF(LEN(TEXT(E159,"000000"))=6,LEFT(TEXT(E159,"000000"),2),""),"")</f>
@@ -17830,7 +17818,7 @@
         <v>891</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F161" s="1" t="str">
         <f aca="false">IF(C161="Singapore",IF(LEN(TEXT(E161,"000000"))=6,LEFT(TEXT(E161,"000000"),2),""),"")</f>
@@ -17846,7 +17834,7 @@
         <v>57</v>
       </c>
       <c r="K161" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L161" s="11" t="s">
         <v>59</v>
@@ -17916,7 +17904,7 @@
         <v>00</v>
       </c>
       <c r="K162" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L162" s="11" t="s">
         <v>59</v>
@@ -17986,7 +17974,7 @@
         <v>00</v>
       </c>
       <c r="K163" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L163" s="11" t="s">
         <v>59</v>
@@ -18052,20 +18040,20 @@
         <v>899</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F164" s="1" t="str">
         <f aca="false">IF(C164="Singapore",IF(LEN(TEXT(E164,"000000"))=6,LEFT(TEXT(E164,"000000"),2),""),"")</f>
         <v>03</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K164" s="11" t="s">
         <v>900</v>
@@ -18134,20 +18122,20 @@
         <v>904</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F165" s="1" t="str">
         <f aca="false">IF(C165="Singapore",IF(LEN(TEXT(E165,"000000"))=6,LEFT(TEXT(E165,"000000"),2),""),"")</f>
         <v>05</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K165" s="11"/>
       <c r="L165" s="11" t="s">
@@ -18175,7 +18163,7 @@
         <v>63</v>
       </c>
       <c r="AK165" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM165" s="12" t="n">
         <v>46311</v>
@@ -18304,13 +18292,13 @@
         <v>19</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K167" s="11" t="s">
         <v>914</v>
@@ -18386,16 +18374,16 @@
         <v>19</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K168" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L168" s="11" t="s">
         <v>59</v>
@@ -18638,13 +18626,13 @@
         <v>12</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K171" s="11" t="s">
         <v>102</v>
@@ -19050,10 +19038,10 @@
         <v>52</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F176" s="1" t="str">
         <f aca="false">IF(C176="Singapore",IF(LEN(TEXT(E176,"000000"))=6,LEFT(TEXT(E176,"000000"),2),""),"")</f>
@@ -19132,23 +19120,23 @@
         <v>52</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F177" s="1" t="str">
         <f aca="false">IF(C177="Singapore",IF(LEN(TEXT(E177,"000000"))=6,LEFT(TEXT(E177,"000000"),2),""),"")</f>
         <v>63</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K177" s="11" t="s">
         <v>960</v>
@@ -19309,13 +19297,13 @@
         <v>44</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K179" s="11" t="s">
         <v>960</v>
@@ -19384,20 +19372,20 @@
         <v>971</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F180" s="1" t="str">
         <f aca="false">IF(C180="Singapore",IF(LEN(TEXT(E180,"000000"))=6,LEFT(TEXT(E180,"000000"),2),""),"")</f>
         <v>03</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K180" s="11" t="s">
         <v>960</v>
@@ -19466,20 +19454,20 @@
         <v>974</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F181" s="1" t="str">
         <f aca="false">IF(C181="Singapore",IF(LEN(TEXT(E181,"000000"))=6,LEFT(TEXT(E181,"000000"),2),""),"")</f>
         <v>05</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K181" s="11" t="s">
         <v>960</v>
@@ -19555,13 +19543,13 @@
         <v>64</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K182" s="11" t="s">
         <v>960</v>
@@ -19877,16 +19865,16 @@
         <v>03</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K186" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L186" s="11" t="s">
         <v>59</v>
@@ -19959,7 +19947,7 @@
         <v>00</v>
       </c>
       <c r="K187" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L187" s="11" t="s">
         <v>59</v>
@@ -20032,13 +20020,13 @@
         <v>18</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K188" s="11" t="s">
         <v>1002</v>
@@ -20123,7 +20111,7 @@
         <v>72</v>
       </c>
       <c r="K189" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L189" s="11" t="s">
         <v>59</v>
@@ -20221,7 +20209,7 @@
         <v>63</v>
       </c>
       <c r="AK190" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM190" s="12" t="n">
         <v>46311</v>
@@ -20267,17 +20255,17 @@
         <v>18</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K191" s="11"/>
       <c r="L191" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M191" s="1" t="n">
         <v>1.300284</v>
@@ -20506,7 +20494,7 @@
         <v>72</v>
       </c>
       <c r="K194" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L194" s="11" t="s">
         <v>59</v>
@@ -20591,7 +20579,7 @@
         <v>72</v>
       </c>
       <c r="K195" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L195" s="11" t="s">
         <v>59</v>
@@ -20667,17 +20655,17 @@
         <v>18</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K196" s="11"/>
       <c r="L196" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M196" s="1" t="n">
         <v>1.30111</v>
@@ -20744,26 +20732,26 @@
       </c>
       <c r="F197" s="1" t="str">
         <f aca="false">IF(C197="Singapore",IF(LEN(TEXT(E197,"000000"))=6,LEFT(TEXT(E197,"000000"),2),""),"")</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>565</v>
+        <v>223</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>566</v>
+        <v>224</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>567</v>
+        <v>225</v>
       </c>
       <c r="K197" s="11"/>
       <c r="L197" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M197" s="1" t="n">
-        <v>1.311361</v>
+        <v>1.300943</v>
       </c>
       <c r="N197" s="1" t="n">
-        <v>103.814987</v>
+        <v>103.859982</v>
       </c>
       <c r="O197" s="11" t="s">
         <v>60</v>
@@ -20783,11 +20771,8 @@
       <c r="AK197" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="AM197" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN197" s="1" t="s">
-        <v>1041</v>
+      <c r="AM197" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT197" s="1" t="s">
         <v>66</v>
@@ -20811,48 +20796,50 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F198" s="1" t="str">
         <f aca="false">IF(C198="Singapore",IF(LEN(TEXT(E198,"000000"))=6,LEFT(TEXT(E198,"000000"),2),""),"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>222</v>
+        <v>339</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>223</v>
+        <v>340</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K198" s="11"/>
+        <v>341</v>
+      </c>
+      <c r="K198" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="L198" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M198" s="1" t="n">
-        <v>1.300943</v>
+        <v>1.304639</v>
       </c>
       <c r="N198" s="1" t="n">
-        <v>103.859982</v>
+        <v>103.854104</v>
       </c>
       <c r="O198" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>62</v>
@@ -20864,10 +20851,13 @@
         <v>63</v>
       </c>
       <c r="AK198" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AM198" s="12" t="s">
         <v>65</v>
+      </c>
+      <c r="AN198" s="1" t="s">
+        <v>1045</v>
       </c>
       <c r="AT198" s="1" t="s">
         <v>66</v>
@@ -20891,10 +20881,10 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>1047</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>1043</v>
       </c>
       <c r="C199" s="11" t="s">
         <v>52</v>
@@ -20907,28 +20897,28 @@
       </c>
       <c r="F199" s="1" t="str">
         <f aca="false">IF(C199="Singapore",IF(LEN(TEXT(E199,"000000"))=6,LEFT(TEXT(E199,"000000"),2),""),"")</f>
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>338</v>
+        <v>830</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>339</v>
+        <v>831</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>340</v>
+        <v>832</v>
       </c>
       <c r="K199" s="11" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L199" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M199" s="1" t="n">
-        <v>1.304639</v>
+        <v>1.398201</v>
       </c>
       <c r="N199" s="1" t="n">
-        <v>103.854104</v>
+        <v>103.873284</v>
       </c>
       <c r="O199" s="11" t="s">
         <v>60</v>
@@ -20946,13 +20936,10 @@
         <v>63</v>
       </c>
       <c r="AK199" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="AM199" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AN199" s="1" t="s">
-        <v>1051</v>
+        <v>1024</v>
+      </c>
+      <c r="AM199" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT199" s="1" t="s">
         <v>66</v>
@@ -20976,44 +20963,44 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F200" s="1" t="str">
         <f aca="false">IF(C200="Singapore",IF(LEN(TEXT(E200,"000000"))=6,LEFT(TEXT(E200,"000000"),2),""),"")</f>
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>830</v>
+        <v>173</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>831</v>
+        <v>174</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>832</v>
+        <v>175</v>
       </c>
       <c r="K200" s="11" t="s">
-        <v>102</v>
+        <v>590</v>
       </c>
       <c r="L200" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M200" s="1" t="n">
-        <v>1.398201</v>
+        <v>1.343191</v>
       </c>
       <c r="N200" s="1" t="n">
-        <v>103.873284</v>
+        <v>103.775138</v>
       </c>
       <c r="O200" s="11" t="s">
         <v>60</v>
@@ -21031,10 +21018,13 @@
         <v>63</v>
       </c>
       <c r="AK200" s="1" t="s">
-        <v>1024</v>
+        <v>176</v>
       </c>
       <c r="AM200" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN200" s="1" t="s">
+        <v>1054</v>
       </c>
       <c r="AT200" s="1" t="s">
         <v>66</v>
@@ -21058,44 +21048,44 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>1056</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>1057</v>
       </c>
       <c r="C201" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>1058</v>
+        <v>68</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>1059</v>
+        <v>69</v>
       </c>
       <c r="F201" s="1" t="str">
         <f aca="false">IF(C201="Singapore",IF(LEN(TEXT(E201,"000000"))=6,LEFT(TEXT(E201,"000000"),2),""),"")</f>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="K201" s="11" t="s">
-        <v>589</v>
+        <v>1057</v>
       </c>
       <c r="L201" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M201" s="1" t="n">
-        <v>1.343191</v>
+        <v>1.372362</v>
       </c>
       <c r="N201" s="1" t="n">
-        <v>103.775138</v>
+        <v>103.949708</v>
       </c>
       <c r="O201" s="11" t="s">
         <v>60</v>
@@ -21113,13 +21103,13 @@
         <v>63</v>
       </c>
       <c r="AK201" s="1" t="s">
-        <v>176</v>
+        <v>838</v>
       </c>
       <c r="AM201" s="12" t="n">
         <v>46311</v>
       </c>
       <c r="AN201" s="1" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AT201" s="1" t="s">
         <v>66</v>
@@ -21143,44 +21133,44 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>68</v>
+        <v>1061</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>69</v>
+        <v>1062</v>
       </c>
       <c r="F202" s="1" t="str">
         <f aca="false">IF(C202="Singapore",IF(LEN(TEXT(E202,"000000"))=6,LEFT(TEXT(E202,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K202" s="11" t="s">
-        <v>1063</v>
+        <v>90</v>
       </c>
       <c r="L202" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M202" s="1" t="n">
-        <v>1.372362</v>
+        <v>1.378679</v>
       </c>
       <c r="N202" s="1" t="n">
-        <v>103.949708</v>
+        <v>103.773381</v>
       </c>
       <c r="O202" s="11" t="s">
         <v>60</v>
@@ -21198,13 +21188,10 @@
         <v>63</v>
       </c>
       <c r="AK202" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="AM202" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN202" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
+      </c>
+      <c r="AM202" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT202" s="1" t="s">
         <v>66</v>
@@ -21228,44 +21215,42 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>1067</v>
+        <v>741</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>1068</v>
+        <v>742</v>
       </c>
       <c r="F203" s="1" t="str">
         <f aca="false">IF(C203="Singapore",IF(LEN(TEXT(E203,"000000"))=6,LEFT(TEXT(E203,"000000"),2),""),"")</f>
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>87</v>
+        <v>365</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>88</v>
+        <v>366</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K203" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="K203" s="11"/>
       <c r="L203" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M203" s="1" t="n">
-        <v>1.378679</v>
+        <v>1.294612</v>
       </c>
       <c r="N203" s="1" t="n">
-        <v>103.773381</v>
+        <v>103.772348</v>
       </c>
       <c r="O203" s="11" t="s">
         <v>60</v>
@@ -21283,10 +21268,10 @@
         <v>63</v>
       </c>
       <c r="AK203" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="AM203" s="12" t="s">
-        <v>65</v>
+        <v>743</v>
+      </c>
+      <c r="AM203" s="12" t="n">
+        <v>46311</v>
       </c>
       <c r="AT203" s="1" t="s">
         <v>66</v>
@@ -21310,48 +21295,48 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>741</v>
+        <v>1068</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>742</v>
+        <v>207</v>
       </c>
       <c r="F204" s="1" t="str">
         <f aca="false">IF(C204="Singapore",IF(LEN(TEXT(E204,"000000"))=6,LEFT(TEXT(E204,"000000"),2),""),"")</f>
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>364</v>
+        <v>55</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>365</v>
+        <v>56</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>366</v>
+        <v>57</v>
       </c>
       <c r="K204" s="11"/>
       <c r="L204" s="11" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="M204" s="1" t="n">
-        <v>1.294612</v>
+        <v>1.323066</v>
       </c>
       <c r="N204" s="1" t="n">
-        <v>103.772348</v>
+        <v>103.854999</v>
       </c>
       <c r="O204" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P204" s="1" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>62</v>
@@ -21363,7 +21348,7 @@
         <v>63</v>
       </c>
       <c r="AK204" s="1" t="s">
-        <v>743</v>
+        <v>1069</v>
       </c>
       <c r="AM204" s="12" t="n">
         <v>46311</v>
@@ -21390,48 +21375,38 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C205" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>206</v>
+        <v>1072</v>
       </c>
       <c r="F205" s="1" t="str">
         <f aca="false">IF(C205="Singapore",IF(LEN(TEXT(E205,"000000"))=6,LEFT(TEXT(E205,"000000"),2),""),"")</f>
-        <v>32</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K205" s="11"/>
+        <v>00</v>
+      </c>
+      <c r="K205" s="11" t="s">
+        <v>1073</v>
+      </c>
       <c r="L205" s="11" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="M205" s="1" t="n">
-        <v>1.323066</v>
+        <v>1.263442</v>
       </c>
       <c r="N205" s="1" t="n">
-        <v>103.854999</v>
+        <v>103.821891</v>
       </c>
       <c r="O205" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P205" s="1" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>62</v>
@@ -21443,7 +21418,7 @@
         <v>63</v>
       </c>
       <c r="AK205" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AM205" s="12" t="n">
         <v>46311</v>
@@ -21470,32 +21445,44 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>1077</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D206" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>1078</v>
       </c>
       <c r="F206" s="1" t="str">
         <f aca="false">IF(C206="Singapore",IF(LEN(TEXT(E206,"000000"))=6,LEFT(TEXT(E206,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>82</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="K206" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="L206" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M206" s="1" t="n">
-        <v>1.263442</v>
+        <v>1.40596</v>
       </c>
       <c r="N206" s="1" t="n">
-        <v>103.821891</v>
+        <v>103.902377</v>
       </c>
       <c r="O206" s="11" t="s">
         <v>60</v>
@@ -21513,7 +21500,7 @@
         <v>63</v>
       </c>
       <c r="AK206" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AM206" s="12" t="n">
         <v>46311</v>
@@ -21540,44 +21527,44 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1083</v>
+        <v>68</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>1084</v>
+        <v>69</v>
       </c>
       <c r="F207" s="1" t="str">
         <f aca="false">IF(C207="Singapore",IF(LEN(TEXT(E207,"000000"))=6,LEFT(TEXT(E207,"000000"),2),""),"")</f>
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1085</v>
+        <v>70</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>492</v>
+        <v>71</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>493</v>
+        <v>72</v>
       </c>
       <c r="K207" s="11" t="s">
-        <v>1086</v>
+        <v>400</v>
       </c>
       <c r="L207" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M207" s="1" t="n">
-        <v>1.40596</v>
+        <v>1.372316</v>
       </c>
       <c r="N207" s="1" t="n">
-        <v>103.902377</v>
+        <v>103.949925</v>
       </c>
       <c r="O207" s="11" t="s">
         <v>60</v>
@@ -21595,10 +21582,13 @@
         <v>63</v>
       </c>
       <c r="AK207" s="1" t="s">
-        <v>1087</v>
+        <v>79</v>
       </c>
       <c r="AM207" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN207" s="1" t="s">
+        <v>1083</v>
       </c>
       <c r="AT207" s="1" t="s">
         <v>66</v>
@@ -21622,44 +21612,32 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>69</v>
+        <v>1086</v>
       </c>
       <c r="F208" s="1" t="str">
         <f aca="false">IF(C208="Singapore",IF(LEN(TEXT(E208,"000000"))=6,LEFT(TEXT(E208,"000000"),2),""),"")</f>
-        <v>51</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I208" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J208" s="1" t="s">
-        <v>72</v>
+        <v>00</v>
       </c>
       <c r="K208" s="11" t="s">
-        <v>399</v>
+        <v>102</v>
       </c>
       <c r="L208" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M208" s="1" t="n">
-        <v>1.372316</v>
+        <v>1.305888</v>
       </c>
       <c r="N208" s="1" t="n">
-        <v>103.949925</v>
+        <v>103.850594</v>
       </c>
       <c r="O208" s="11" t="s">
         <v>60</v>
@@ -21677,13 +21655,10 @@
         <v>63</v>
       </c>
       <c r="AK208" s="1" t="s">
-        <v>79</v>
+        <v>1087</v>
       </c>
       <c r="AM208" s="12" t="n">
         <v>46311</v>
-      </c>
-      <c r="AN208" s="1" t="s">
-        <v>1089</v>
       </c>
       <c r="AT208" s="1" t="s">
         <v>66</v>
@@ -21707,32 +21682,44 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1092</v>
+        <v>68</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="F209" s="1" t="str">
         <f aca="false">IF(C209="Singapore",IF(LEN(TEXT(E209,"000000"))=6,LEFT(TEXT(E209,"000000"),2),""),"")</f>
-        <v>00</v>
+        <v>51</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="K209" s="11" t="s">
-        <v>102</v>
+        <v>415</v>
       </c>
       <c r="L209" s="11" t="s">
         <v>59</v>
       </c>
       <c r="M209" s="1" t="n">
-        <v>1.305888</v>
+        <v>1.372381</v>
       </c>
       <c r="N209" s="1" t="n">
-        <v>103.850594</v>
+        <v>103.949343</v>
       </c>
       <c r="O209" s="11" t="s">
         <v>60</v>
@@ -21750,10 +21737,13 @@
         <v>63</v>
       </c>
       <c r="AK209" s="1" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="AM209" s="12" t="n">
         <v>46311</v>
+      </c>
+      <c r="AN209" s="1" t="s">
+        <v>1091</v>
       </c>
       <c r="AT209" s="1" t="s">
         <v>66</v>
@@ -21777,50 +21767,48 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>68</v>
+        <v>1061</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>69</v>
+        <v>1062</v>
       </c>
       <c r="F210" s="1" t="str">
         <f aca="false">IF(C210="Singapore",IF(LEN(TEXT(E210,"000000"))=6,LEFT(TEXT(E210,"000000"),2),""),"")</f>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K210" s="11" t="s">
-        <v>414</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="K210" s="11"/>
       <c r="L210" s="11" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="M210" s="1" t="n">
-        <v>1.372381</v>
+        <v>1.378723</v>
       </c>
       <c r="N210" s="1" t="n">
-        <v>103.949343</v>
+        <v>103.773386</v>
       </c>
       <c r="O210" s="11" t="s">
         <v>60</v>
       </c>
       <c r="P210" s="1" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>62</v>
@@ -21832,13 +21820,10 @@
         <v>63</v>
       </c>
       <c r="AK210" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="AM210" s="12" t="n">
-        <v>46311</v>
-      </c>
-      <c r="AN210" s="1" t="s">
-        <v>1096</v>
+        <v>1063</v>
+      </c>
+      <c r="AM210" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="AT210" s="1" t="s">
         <v>66</v>
@@ -21861,84 +21846,11 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C211" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F211" s="1" t="str">
-        <f aca="false">IF(C211="Singapore",IF(LEN(TEXT(E211,"000000"))=6,LEFT(TEXT(E211,"000000"),2),""),"")</f>
-        <v>67</v>
-      </c>
-      <c r="H211" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I211" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J211" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="C211" s="11"/>
       <c r="K211" s="11"/>
-      <c r="L211" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="M211" s="1" t="n">
-        <v>1.378723</v>
-      </c>
-      <c r="N211" s="1" t="n">
-        <v>103.773386</v>
-      </c>
-      <c r="O211" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="P211" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R211" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AH211" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI211" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK211" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="AM211" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AT211" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AU211" s="1" t="str">
-        <f aca="false">IF(OR(AT211=TRUE(),AT211="TRUE"),"This sample listing is provided solely to demonstrate the directory interface. It does not represent a live declaration, verification, endorsement or participating establishment.","")</f>
-        <v/>
-      </c>
-      <c r="AV211" s="1" t="str">
-        <f aca="false">IF(OR(A211="",B211="",C211="",D211=""),"Missing required fields",IF(NOT(AND(ISNUMBER(M211),ISNUMBER(N211))),"Missing coordinates","Complete"))</f>
-        <v>Complete</v>
-      </c>
-      <c r="AW211" s="1" t="str">
-        <f aca="false">IF(AND(ISNUMBER(M211),ISNUMBER(N211)),"Ready","Coordinates required")</f>
-        <v>Ready</v>
-      </c>
-      <c r="AX211" s="1" t="str">
-        <f aca="false">IF(OR(AT211=TRUE(),AT211="TRUE"),"Demo record",IF(A211="","Missing ID",IF(B211="","Missing name",IF(NOT(AND(ISNUMBER(M211),ISNUMBER(N211))),"Coordinates required","Ready for publication"))))</f>
-        <v>Ready for publication</v>
-      </c>
+      <c r="L211" s="11"/>
+      <c r="O211" s="11"/>
+      <c r="AM211" s="12"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C212" s="11"/>
@@ -26818,290 +26730,290 @@
         <v>9</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="E2" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="E3" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="E4" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="E5" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="E6" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>193</v>
-      </c>
       <c r="E7" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>238</v>
-      </c>
       <c r="E8" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>238</v>
-      </c>
       <c r="E9" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="E10" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="E11" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>364</v>
-      </c>
       <c r="E12" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>364</v>
-      </c>
       <c r="E13" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>364</v>
-      </c>
       <c r="E14" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>212</v>
-      </c>
       <c r="E15" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>212</v>
-      </c>
       <c r="E16" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="B17" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>212</v>
-      </c>
       <c r="E17" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>602</v>
@@ -27113,182 +27025,182 @@
         <v>601</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="B19" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>222</v>
-      </c>
       <c r="E19" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="B20" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>222</v>
-      </c>
       <c r="E20" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="B21" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>338</v>
-      </c>
       <c r="E21" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>338</v>
-      </c>
       <c r="E22" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="B25" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>565</v>
-      </c>
       <c r="E25" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="B26" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>565</v>
-      </c>
       <c r="E26" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="B27" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="D27" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>565</v>
-      </c>
       <c r="E27" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>109</v>
@@ -27300,12 +27212,12 @@
         <v>108</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>109</v>
@@ -27317,12 +27229,12 @@
         <v>108</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>109</v>
@@ -27334,12 +27246,12 @@
         <v>926</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>56</v>
@@ -27348,15 +27260,15 @@
         <v>57</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>56</v>
@@ -27368,12 +27280,12 @@
         <v>55</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>56</v>
@@ -27385,216 +27297,216 @@
         <v>55</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>186</v>
-      </c>
       <c r="E37" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="B38" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>186</v>
-      </c>
       <c r="E38" s="14" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="B39" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>519</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>518</v>
-      </c>
       <c r="E39" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="B40" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>519</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>518</v>
-      </c>
       <c r="E40" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="B41" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="D41" s="14" t="s">
         <v>519</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>518</v>
-      </c>
       <c r="E41" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>642</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="B43" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D43" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>267</v>
-      </c>
       <c r="E43" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="B44" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D44" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>267</v>
-      </c>
       <c r="E44" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="B45" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>267</v>
-      </c>
       <c r="E45" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>157</v>
@@ -27606,12 +27518,12 @@
         <v>156</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>157</v>
@@ -27623,12 +27535,12 @@
         <v>156</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>157</v>
@@ -27640,12 +27552,12 @@
         <v>156</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>165</v>
@@ -27657,12 +27569,12 @@
         <v>164</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>165</v>
@@ -27674,12 +27586,12 @@
         <v>164</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>71</v>
@@ -27691,12 +27603,12 @@
         <v>70</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>71</v>
@@ -27708,97 +27620,97 @@
         <v>70</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="B54" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="D54" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>491</v>
-      </c>
       <c r="E54" s="14" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="B55" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="D55" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>491</v>
-      </c>
       <c r="E55" s="14" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="B57" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C57" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>313</v>
-      </c>
       <c r="E57" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="B58" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="D58" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>313</v>
-      </c>
       <c r="E58" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>174</v>
@@ -27807,15 +27719,15 @@
         <v>175</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>174</v>
@@ -27827,97 +27739,97 @@
         <v>173</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B63" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C63" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="E63" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="B64" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="E64" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B65" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C65" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="E65" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>88</v>
@@ -27929,12 +27841,12 @@
         <v>140</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>88</v>
@@ -27946,12 +27858,12 @@
         <v>140</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>88</v>
@@ -27963,12 +27875,12 @@
         <v>87</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>88</v>
@@ -27980,97 +27892,97 @@
         <v>87</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>934</v>
@@ -28079,49 +27991,49 @@
         <v>935</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="B76" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="D76" s="14" t="s">
         <v>582</v>
       </c>
-      <c r="C76" s="14" t="s">
-        <v>583</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>581</v>
-      </c>
       <c r="E76" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>934</v>
@@ -28130,15 +28042,15 @@
         <v>935</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>934</v>
@@ -28150,12 +28062,12 @@
         <v>933</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>831</v>
@@ -28167,12 +28079,12 @@
         <v>830</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>831</v>
@@ -28184,12 +28096,12 @@
         <v>830</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>165</v>
@@ -28198,44 +28110,44 @@
         <v>166</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
   </sheetData>
@@ -28277,7 +28189,7 @@
         <v>14</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>18</v>
@@ -28294,36 +28206,36 @@
         <v>52</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>59</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>60</v>
@@ -28332,72 +28244,72 @@
         <v>66</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>112</v>
@@ -28405,40 +28317,40 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="16" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28446,37 +28358,37 @@
         <v>927</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
     </row>
   </sheetData>
@@ -28504,42 +28416,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
   </sheetData>
